--- a/Ежедневная статистика.xlsx
+++ b/Ежедневная статистика.xlsx
@@ -2,12 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Статистика" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,17 +15,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0 &quot;₽&quot;"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -64,19 +62,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD1F5D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFACCD1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -438,212 +452,1565 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="27" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="18.7109375" customWidth="1" min="1" max="1"/>
+    <col width="12.7109375" customWidth="1" min="2" max="2"/>
+    <col width="15.7109375" customWidth="1" min="3" max="3"/>
+    <col width="16.7109375" customWidth="1" min="4" max="5"/>
+    <col width="17.7109375" customWidth="1" min="6" max="6"/>
+    <col width="9.7109375" customWidth="1" min="7" max="7"/>
+    <col width="22.7109375" customWidth="1" min="8" max="9"/>
+    <col width="26.7109375" customWidth="1" min="10" max="10"/>
+    <col width="29.7109375" customWidth="1" min="11" max="11"/>
+    <col width="27.7109375" customWidth="1" min="12" max="12"/>
+    <col width="24.7109375" customWidth="1" min="13" max="13"/>
+    <col width="25.7109375" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Обновлено</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Заказано, шт.</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Заказано, руб.</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Выкуплено, шт.</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Выкуплено, руб.</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Показов</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Переходов в карточки</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Добавлений в корзину</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Средняя конверсия в клик</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Средняя конверсия в корзину</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Средняя конверсия в заказ</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Средний процент выкупа</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Добавлений в Отложенные</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>19.03.2026 14:34</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>18.02.2026</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 07:42</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>474</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>557737</v>
+        <v>326</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>396591</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>473</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>557037</v>
+        <v>324</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>394239</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>21029</v>
+        <v>302960</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>1687</v>
+        <v>19200</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>9.808080808080808</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>36.98611111111111</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>95.47887323943662</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>503</v>
+        <v>1345</v>
+      </c>
+      <c r="J2" s="5">
+        <f>IFERROR(H2/G2,0)</f>
+        <v/>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0.08371428571428571</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>0.3780821917808219</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>0.9608219178082191</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>457</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>19.03.2026 14:34</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>19.02.2026</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 07:45</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>488</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>590523</v>
+        <v>367</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>444303</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>487</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>585887</v>
+        <v>367</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>444303</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>21588</v>
+        <v>326685</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1587</v>
+        <v>19471</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>42.12</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>92.35714285714286</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>471</v>
+        <v>1399</v>
+      </c>
+      <c r="J3" s="5">
+        <f>IFERROR(H3/G3,0)</f>
+        <v/>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0.0887962962962963</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>0.9597183098591549</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>455</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>19.03.2026 14:34</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>20.02.2026</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 07:47</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>479</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>595217</v>
+        <v>310</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>376271</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>479</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>595217</v>
+        <v>309</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>374981</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>19155</v>
+        <v>265545</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1493</v>
+        <v>16506</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>8.397959183673469</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>44.76923076923077</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>95.16049382716049</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>470</v>
+        <v>1263</v>
+      </c>
+      <c r="J4" s="5">
+        <f>IFERROR(H4/G4,0)</f>
+        <v/>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0.08467391304347827</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0.3931884057971015</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0.9571428571428571</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 07:49</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>309</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>394711</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>309</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>394711</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>222525</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>16313</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>1214</v>
+      </c>
+      <c r="J5" s="5">
+        <f>IFERROR(H5/G5,0)</f>
+        <v/>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.09789999999999999</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0.3329166666666666</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0.9594520547945206</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 07:51</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>27.02.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>313</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>401453</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>312</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>399825</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>259389</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>16109</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1208</v>
+      </c>
+      <c r="J6" s="5">
+        <f>IFERROR(H6/G6,0)</f>
+        <v/>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0.07978494623655914</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0.4064705882352941</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0.9571428571428571</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 07:53</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>322</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>420954</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>321</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>419594</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>273232</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>17369</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>1284</v>
+      </c>
+      <c r="J7" s="5">
+        <f>IFERROR(H7/G7,0)</f>
+        <v/>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0.0728421052631579</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>0.3978787878787879</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>0.9509375</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 09:12</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>01.03.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>371</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>490574</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>368</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>486963</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>245809</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>17517</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>1351</v>
+      </c>
+      <c r="J8" s="5">
+        <f>IFERROR(H8/G8,0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0.0775</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0.4186567164179105</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0.9651470588235295</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 09:15</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>02.03.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>341</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>426620</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>340</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>424806</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>218082</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>15540</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>1103</v>
+      </c>
+      <c r="J9" s="5">
+        <f>IFERROR(H9/G9,0)</f>
+        <v/>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0.07556701030927834</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>0.5231944444444444</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>0.9551470588235295</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 09:17</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>03.03.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>387</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>501848</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>385</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>498827</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>224837</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>15990</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J10" s="5">
+        <f>IFERROR(H10/G10,0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0.08624999999999999</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0.4166233766233766</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0.9718666666666667</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 09:19</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>04.03.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>324</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>431269</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>426868</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>212892</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>15275</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>1196</v>
+      </c>
+      <c r="J11" s="5">
+        <f>IFERROR(H11/G11,0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.1047422680412371</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>0.3683333333333333</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0.9494366197183099</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 09:20</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>05.03.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>353</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>446401</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>351</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>442751</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>200422</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>14431</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>1106</v>
+      </c>
+      <c r="J12" s="5">
+        <f>IFERROR(H12/G12,0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0.08386138613861385</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0.4845833333333334</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 09:21</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>06.03.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>317</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>432330</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>313</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>427795</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>192265</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>13970</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1062</v>
+      </c>
+      <c r="J13" s="5">
+        <f>IFERROR(H13/G13,0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>0.4204411764705883</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0.9622727272727274</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 09:23</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>369566</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>362004</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>272627</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>16303</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="J14" s="5">
+        <f>IFERROR(H14/G14,0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0.0799009900990099</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>0.4041176470588235</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0.9534328358208956</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 09:28</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>315327</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>228</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>307946</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>220115</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>13611</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>981</v>
+      </c>
+      <c r="J15" s="5">
+        <f>IFERROR(H15/G15,0)</f>
+        <v/>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.08353535353535353</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0.4074242424242424</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0.9736923076923076</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 09:38</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>339590</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>253</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>323574</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>239321</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>15623</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>1072</v>
+      </c>
+      <c r="J16" s="5">
+        <f>IFERROR(H16/G16,0)</f>
+        <v/>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0.07648936170212765</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>0.3862857142857143</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>0.9782608695652173</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>24.03.2026 09:00</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>245</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>320402</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>237</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>310645</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>165823</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>12385</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>963</v>
+      </c>
+      <c r="J17" s="5">
+        <f>IFERROR(H17/G17,0)</f>
+        <v/>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.08858585858585859</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>0.4930434782608695</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0.9457352941176471</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 09:41</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>11.03.2026</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>182</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>232419</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>212968</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>173565</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>11624</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>921</v>
+      </c>
+      <c r="J18" s="5">
+        <f>IFERROR(H18/G18,0)</f>
+        <v/>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.108804347826087</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0.3730508474576271</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>0.9698245614035088</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 09:42</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>12.03.2026</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>209</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>282434</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>259422</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>164251</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>11117</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>793</v>
+      </c>
+      <c r="J19" s="5">
+        <f>IFERROR(H19/G19,0)</f>
+        <v/>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0.07782608695652174</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0.4380701754385965</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0.9431481481481481</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 09:43</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>13.03.2026</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>311866</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>209</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>271893</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>182081</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>12785</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>975</v>
+      </c>
+      <c r="J20" s="5">
+        <f>IFERROR(H20/G20,0)</f>
+        <v/>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0.09148936170212765</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0.3601639344262295</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0.9650847457627119</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 09:44</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>14.03.2026</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>225</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>305772</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>260589</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>312695</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>16261</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>1102</v>
+      </c>
+      <c r="J21" s="5">
+        <f>IFERROR(H21/G21,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0.104020618556701</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>0.4171428571428571</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>0.9449230769230769</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026 09:45</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>15.03.2026</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>287712</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>251113</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>245765</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>13922</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>1070</v>
+      </c>
+      <c r="J22" s="5">
+        <f>IFERROR(H22/G22,0)</f>
+        <v/>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0.0943157894736842</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>0.3650793650793651</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>0.9403508771929825</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>24.03.2026 09:05</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>16.03.2026</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>223</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>288894</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>226731</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>224933</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>12906</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>924</v>
+      </c>
+      <c r="J23" s="5">
+        <f>IFERROR(H23/G23,0)</f>
+        <v/>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0.1007142857142857</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>0.3946551724137931</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0.9828</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>24.03.2026 09:06</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>17.03.2026</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>211</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>274216</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>189086</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>216194</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>11574</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>848</v>
+      </c>
+      <c r="J24" s="5">
+        <f>IFERROR(H24/G24,0)</f>
+        <v/>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0.08456521739130435</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0.45375</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>0.9747058823529412</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>24.03.2026 09:07</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>18.03.2026</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>257085</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>178639</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>145959</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>10270</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>851</v>
+      </c>
+      <c r="J25" s="5">
+        <f>IFERROR(H25/G25,0)</f>
+        <v/>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0.114020618556701</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>0.4131746031746031</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>0.9796296296296296</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>24.03.2026 09:08</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>19.03.2026</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>243320</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>151049</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>120611</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>9584</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>779</v>
+      </c>
+      <c r="J26" s="5">
+        <f>IFERROR(H26/G26,0)</f>
+        <v/>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0.09440860215053765</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0.4246666666666667</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0.9967307692307692</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>24.03.2026 09:09</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>210756</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>109656</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>120093</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>9272</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>713</v>
+      </c>
+      <c r="J27" s="5">
+        <f>IFERROR(H27/G27,0)</f>
+        <v/>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>0.4106896551724138</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>0.9722222222222223</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>24.03.2026 13:42</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>21.03.2026</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>252421</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>129162</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>104174</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>8704</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>705</v>
+      </c>
+      <c r="J28" s="5">
+        <f>IFERROR(H28/G28,0)</f>
+        <v/>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0.09926829268292683</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>0.3877586206896552</v>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>0.9870731707317073</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>24.03.2026 13:43</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>22.03.2026</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>207</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>276845</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>55548</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>124434</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>10136</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>784</v>
+      </c>
+      <c r="J29" s="5">
+        <f>IFERROR(H29/G29,0)</f>
+        <v/>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0.1098958333333333</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>0.4292537313432836</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>24.03.2026 13:43</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>23.03.2026</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>211049</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>10776</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>115729</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>8906</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>688</v>
+      </c>
+      <c r="J30" s="5">
+        <f>IFERROR(H30/G30,0)</f>
+        <v/>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0.09966666666666667</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0.3960377358490566</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="C3:C30">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>C3&gt;C2</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>C3&lt;C2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G30">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>G3&gt;G2</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>G3&lt;G2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I30">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>I3&gt;I2</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="1">
+      <formula>I3&lt;I2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J30">
+    <cfRule type="expression" priority="7" dxfId="0">
+      <formula>J3&gt;J2</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="1">
+      <formula>J3&lt;J2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K30">
+    <cfRule type="expression" priority="9" dxfId="0">
+      <formula>K3&gt;K2</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="1">
+      <formula>K3&lt;K2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L30">
+    <cfRule type="expression" priority="11" dxfId="0">
+      <formula>L3&gt;L2</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="1">
+      <formula>L3&lt;L2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Ежедневная статистика.xlsx
+++ b/Ежедневная статистика.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dergacevad\Folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EFB4BC-7F06-4EBC-B4D8-9D56F325009C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A9BDFD-09A3-4835-8EAB-D4F63821DCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="94">
   <si>
     <t>Обновлено</t>
   </si>
@@ -112,15 +112,12 @@
     <t>02.03.2026</t>
   </si>
   <si>
-    <t>23.03.2026 09:17</t>
+    <t>31.03.2026 14:35</t>
   </si>
   <si>
     <t>03.03.2026</t>
   </si>
   <si>
-    <t>23.03.2026 09:19</t>
-  </si>
-  <si>
     <t>04.03.2026</t>
   </si>
   <si>
@@ -130,61 +127,52 @@
     <t>05.03.2026</t>
   </si>
   <si>
-    <t>23.03.2026 09:21</t>
+    <t>31.03.2026 14:36</t>
   </si>
   <si>
     <t>06.03.2026</t>
   </si>
   <si>
-    <t>23.03.2026 09:23</t>
+    <t>31.03.2026 14:37</t>
   </si>
   <si>
     <t>07.03.2026</t>
   </si>
   <si>
-    <t>23.03.2026 09:28</t>
+    <t>31.03.2026 14:38</t>
   </si>
   <si>
     <t>08.03.2026</t>
   </si>
   <si>
-    <t>23.03.2026 09:38</t>
-  </si>
-  <si>
     <t>09.03.2026</t>
   </si>
   <si>
-    <t>25.03.2026 12:47</t>
+    <t>31.03.2026 14:39</t>
   </si>
   <si>
     <t>10.03.2026</t>
   </si>
   <si>
-    <t>25.03.2026 12:48</t>
-  </si>
-  <si>
     <t>11.03.2026</t>
   </si>
   <si>
-    <t>26.03.2026 07:38</t>
+    <t>31.03.2026 14:40</t>
   </si>
   <si>
     <t>12.03.2026</t>
   </si>
   <si>
-    <t>25.03.2026 12:49</t>
-  </si>
-  <si>
     <t>13.03.2026</t>
   </si>
   <si>
-    <t>26.03.2026 07:39</t>
+    <t>31.03.2026 14:41</t>
   </si>
   <si>
     <t>14.03.2026</t>
   </si>
   <si>
-    <t>26.03.2026 07:40</t>
+    <t>31.03.2026 14:42</t>
   </si>
   <si>
     <t>15.03.2026</t>
@@ -193,22 +181,25 @@
     <t>16.03.2026</t>
   </si>
   <si>
-    <t>26.03.2026 07:41</t>
+    <t>31.03.2026 08:59</t>
   </si>
   <si>
     <t>17.03.2026</t>
   </si>
   <si>
-    <t>26.03.2026 07:42</t>
+    <t>02.04.2026 10:53</t>
   </si>
   <si>
     <t>18.03.2026</t>
   </si>
   <si>
+    <t>02.04.2026 10:54</t>
+  </si>
+  <si>
     <t>19.03.2026</t>
   </si>
   <si>
-    <t>26.03.2026 07:43</t>
+    <t>02.04.2026 10:55</t>
   </si>
   <si>
     <t>20.03.2026</t>
@@ -217,22 +208,100 @@
     <t>21.03.2026</t>
   </si>
   <si>
-    <t>26.03.2026 07:44</t>
+    <t>07.04.2026 09:40</t>
   </si>
   <si>
     <t>22.03.2026</t>
   </si>
   <si>
+    <t>08.04.2026 11:25</t>
+  </si>
+  <si>
     <t>23.03.2026</t>
   </si>
   <si>
-    <t>26.03.2026 07:45</t>
+    <t>08.04.2026 07:23</t>
   </si>
   <si>
     <t>24.03.2026</t>
   </si>
   <si>
+    <t>10.04.2026 06:54</t>
+  </si>
+  <si>
     <t>25.03.2026</t>
+  </si>
+  <si>
+    <t>10.04.2026 06:55</t>
+  </si>
+  <si>
+    <t>26.03.2026</t>
+  </si>
+  <si>
+    <t>10.04.2026 06:56</t>
+  </si>
+  <si>
+    <t>27.03.2026</t>
+  </si>
+  <si>
+    <t>28.03.2026</t>
+  </si>
+  <si>
+    <t>10.04.2026 06:57</t>
+  </si>
+  <si>
+    <t>29.03.2026</t>
+  </si>
+  <si>
+    <t>30.03.2026</t>
+  </si>
+  <si>
+    <t>10.04.2026 06:58</t>
+  </si>
+  <si>
+    <t>31.03.2026</t>
+  </si>
+  <si>
+    <t>10.04.2026 06:59</t>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+  </si>
+  <si>
+    <t>02.04.2026</t>
+  </si>
+  <si>
+    <t>10.04.2026 07:00</t>
+  </si>
+  <si>
+    <t>03.04.2026</t>
+  </si>
+  <si>
+    <t>04.04.2026</t>
+  </si>
+  <si>
+    <t>10.04.2026 07:01</t>
+  </si>
+  <si>
+    <t>05.04.2026</t>
+  </si>
+  <si>
+    <t>06.04.2026</t>
+  </si>
+  <si>
+    <t>10.04.2026 07:02</t>
+  </si>
+  <si>
+    <t>07.04.2026</t>
+  </si>
+  <si>
+    <t>10.04.2026 07:03</t>
+  </si>
+  <si>
+    <t>08.04.2026</t>
+  </si>
+  <si>
+    <t>09.04.2026</t>
   </si>
 </sst>
 </file>
@@ -651,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -741,7 +810,7 @@
         <v>1345</v>
       </c>
       <c r="J2" s="5">
-        <f t="shared" ref="J2:J32" si="0">IFERROR(H2/G2,0)</f>
+        <f t="shared" ref="J2:J47" si="0">IFERROR(H2/G2,0)</f>
         <v>6.337470293108001E-2</v>
       </c>
       <c r="K2" s="5">
@@ -1080,16 +1149,16 @@
         <v>31</v>
       </c>
       <c r="C10" s="3">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D10" s="4">
-        <v>501848</v>
+        <v>500456</v>
       </c>
       <c r="E10" s="3">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F10" s="4">
-        <v>498827</v>
+        <v>500456</v>
       </c>
       <c r="G10" s="3">
         <v>224837</v>
@@ -1111,7 +1180,7 @@
         <v>0.41662337662337662</v>
       </c>
       <c r="M10" s="5">
-        <v>0.97186666666666666</v>
+        <v>0.97053333333333325</v>
       </c>
       <c r="N10" s="3">
         <v>328</v>
@@ -1119,22 +1188,22 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="C11" s="3">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D11" s="4">
-        <v>431269</v>
+        <v>429877</v>
       </c>
       <c r="E11" s="3">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F11" s="4">
-        <v>426868</v>
+        <v>427768</v>
       </c>
       <c r="G11" s="3">
         <v>212892</v>
@@ -1156,7 +1225,7 @@
         <v>0.36833333333333329</v>
       </c>
       <c r="M11" s="5">
-        <v>0.94943661971830995</v>
+        <v>0.94929577464788739</v>
       </c>
       <c r="N11" s="3">
         <v>351</v>
@@ -1164,10 +1233,10 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="C12" s="3">
         <v>353</v>
@@ -1209,22 +1278,22 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="C13" s="3">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D13" s="4">
-        <v>432330</v>
+        <v>428485</v>
       </c>
       <c r="E13" s="3">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F13" s="4">
-        <v>427795</v>
+        <v>428485</v>
       </c>
       <c r="G13" s="3">
         <v>192265</v>
@@ -1246,7 +1315,7 @@
         <v>0.42044117647058832</v>
       </c>
       <c r="M13" s="5">
-        <v>0.96227272727272739</v>
+        <v>0.95833333333333326</v>
       </c>
       <c r="N13" s="3">
         <v>341</v>
@@ -1254,22 +1323,22 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="C14" s="3">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D14" s="4">
-        <v>369566</v>
+        <v>365763</v>
       </c>
       <c r="E14" s="3">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F14" s="4">
-        <v>362004</v>
+        <v>364371</v>
       </c>
       <c r="G14" s="3">
         <v>272627</v>
@@ -1291,7 +1360,7 @@
         <v>0.40411764705882353</v>
       </c>
       <c r="M14" s="5">
-        <v>0.95343283582089555</v>
+        <v>0.94507462686567167</v>
       </c>
       <c r="N14" s="3">
         <v>424</v>
@@ -1299,22 +1368,22 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="C15" s="3">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D15" s="4">
-        <v>315327</v>
+        <v>313008</v>
       </c>
       <c r="E15" s="3">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F15" s="4">
-        <v>307946</v>
+        <v>308896</v>
       </c>
       <c r="G15" s="3">
         <v>220115</v>
@@ -1336,7 +1405,7 @@
         <v>0.40742424242424241</v>
       </c>
       <c r="M15" s="5">
-        <v>0.97369230769230763</v>
+        <v>0.97292307692307689</v>
       </c>
       <c r="N15" s="3">
         <v>309</v>
@@ -1344,22 +1413,22 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D16" s="4">
-        <v>339590</v>
+        <v>336826</v>
       </c>
       <c r="E16" s="3">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="F16" s="4">
-        <v>323574</v>
+        <v>333593</v>
       </c>
       <c r="G16" s="3">
         <v>239321</v>
@@ -1381,7 +1450,7 @@
         <v>0.38628571428571429</v>
       </c>
       <c r="M16" s="5">
-        <v>0.97826086956521729</v>
+        <v>0.96785714285714297</v>
       </c>
       <c r="N16" s="3">
         <v>387</v>
@@ -1389,10 +1458,10 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" s="3">
         <v>243</v>
@@ -1401,10 +1470,10 @@
         <v>317649</v>
       </c>
       <c r="E17" s="3">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F17" s="4">
-        <v>313429</v>
+        <v>315364</v>
       </c>
       <c r="G17" s="3">
         <v>165823</v>
@@ -1426,7 +1495,7 @@
         <v>0.49304347826086953</v>
       </c>
       <c r="M17" s="5">
-        <v>0.9425</v>
+        <v>0.94449275362318841</v>
       </c>
       <c r="N17" s="3">
         <v>347</v>
@@ -1434,22 +1503,22 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C18" s="3">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D18" s="4">
-        <v>230809</v>
+        <v>225292</v>
       </c>
       <c r="E18" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F18" s="4">
-        <v>220069</v>
+        <v>221194</v>
       </c>
       <c r="G18" s="3">
         <v>173565</v>
@@ -1471,7 +1540,7 @@
         <v>0.37305084745762712</v>
       </c>
       <c r="M18" s="5">
-        <v>0.96719298245614038</v>
+        <v>0.96245614035087723</v>
       </c>
       <c r="N18" s="3">
         <v>338</v>
@@ -1479,22 +1548,22 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C19" s="3">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D19" s="4">
-        <v>282434</v>
+        <v>275339</v>
       </c>
       <c r="E19" s="3">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F19" s="4">
-        <v>267873</v>
+        <v>273097</v>
       </c>
       <c r="G19" s="3">
         <v>164251</v>
@@ -1516,7 +1585,7 @@
         <v>0.4380701754385965</v>
       </c>
       <c r="M19" s="5">
-        <v>0.94517857142857142</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="N19" s="3">
         <v>292</v>
@@ -1524,22 +1593,22 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C20" s="3">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D20" s="4">
-        <v>310966</v>
+        <v>296651</v>
       </c>
       <c r="E20" s="3">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="F20" s="4">
-        <v>276901</v>
+        <v>286784</v>
       </c>
       <c r="G20" s="3">
         <v>182081</v>
@@ -1561,7 +1630,7 @@
         <v>0.36016393442622952</v>
       </c>
       <c r="M20" s="5">
-        <v>0.96525423728813564</v>
+        <v>0.93796610169491534</v>
       </c>
       <c r="N20" s="3">
         <v>390</v>
@@ -1569,22 +1638,22 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C21" s="3">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D21" s="4">
-        <v>305772</v>
+        <v>302147</v>
       </c>
       <c r="E21" s="3">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F21" s="4">
-        <v>282335</v>
+        <v>287954</v>
       </c>
       <c r="G21" s="3">
         <v>312695</v>
@@ -1606,7 +1675,7 @@
         <v>0.41714285714285709</v>
       </c>
       <c r="M21" s="5">
-        <v>0.95385714285714285</v>
+        <v>0.95352112676056333</v>
       </c>
       <c r="N21" s="3">
         <v>436</v>
@@ -1614,22 +1683,22 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C22" s="3">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D22" s="4">
-        <v>286812</v>
+        <v>285452</v>
       </c>
       <c r="E22" s="3">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="F22" s="4">
-        <v>267195</v>
+        <v>275815</v>
       </c>
       <c r="G22" s="3">
         <v>245765</v>
@@ -1651,7 +1720,7 @@
         <v>0.36507936507936511</v>
       </c>
       <c r="M22" s="5">
-        <v>0.9374137931034483</v>
+        <v>0.93333333333333324</v>
       </c>
       <c r="N22" s="3">
         <v>316</v>
@@ -1659,22 +1728,22 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C23" s="3">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D23" s="4">
-        <v>283986</v>
+        <v>276510</v>
       </c>
       <c r="E23" s="3">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="F23" s="4">
-        <v>242957</v>
+        <v>260239</v>
       </c>
       <c r="G23" s="3">
         <v>224933</v>
@@ -1696,7 +1765,7 @@
         <v>0.39465517241379311</v>
       </c>
       <c r="M23" s="5">
-        <v>0.97499999999999998</v>
+        <v>0.96309090909090911</v>
       </c>
       <c r="N23" s="3">
         <v>361</v>
@@ -1704,22 +1773,22 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C24" s="3">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D24" s="4">
-        <v>271732</v>
+        <v>268105</v>
       </c>
       <c r="E24" s="3">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="F24" s="4">
-        <v>216887</v>
+        <v>245592</v>
       </c>
       <c r="G24" s="3">
         <v>216194</v>
@@ -1741,7 +1810,7 @@
         <v>0.45374999999999999</v>
       </c>
       <c r="M24" s="5">
-        <v>0.97074074074074079</v>
+        <v>0.96392857142857136</v>
       </c>
       <c r="N24" s="3">
         <v>296</v>
@@ -1749,22 +1818,22 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C25" s="3">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D25" s="4">
-        <v>255545</v>
+        <v>244036</v>
       </c>
       <c r="E25" s="3">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="F25" s="4">
-        <v>195972</v>
+        <v>228774</v>
       </c>
       <c r="G25" s="3">
         <v>145959</v>
@@ -1786,7 +1855,7 @@
         <v>0.41317460317460308</v>
       </c>
       <c r="M25" s="5">
-        <v>0.97892857142857137</v>
+        <v>0.95517241379310347</v>
       </c>
       <c r="N25" s="3">
         <v>268</v>
@@ -1794,22 +1863,22 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C26" s="3">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D26" s="4">
-        <v>243320</v>
+        <v>236892</v>
       </c>
       <c r="E26" s="3">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="F26" s="4">
-        <v>179706</v>
+        <v>217864</v>
       </c>
       <c r="G26" s="3">
         <v>120611</v>
@@ -1831,7 +1900,7 @@
         <v>0.42449999999999999</v>
       </c>
       <c r="M26" s="5">
-        <v>0.99685185185185188</v>
+        <v>0.98421052631578942</v>
       </c>
       <c r="N26" s="3">
         <v>271</v>
@@ -1839,22 +1908,22 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C27" s="3">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D27" s="4">
-        <v>205892</v>
+        <v>201511</v>
       </c>
       <c r="E27" s="3">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="F27" s="4">
-        <v>146356</v>
+        <v>179934</v>
       </c>
       <c r="G27" s="3">
         <v>120093</v>
@@ -1876,7 +1945,7 @@
         <v>0.41068965517241379</v>
       </c>
       <c r="M27" s="5">
-        <v>0.94374999999999998</v>
+        <v>0.95018518518518524</v>
       </c>
       <c r="N27" s="3">
         <v>269</v>
@@ -1884,22 +1953,22 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C28" s="3">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D28" s="4">
-        <v>248331</v>
+        <v>243859</v>
       </c>
       <c r="E28" s="3">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="F28" s="4">
-        <v>191536</v>
+        <v>231958</v>
       </c>
       <c r="G28" s="3">
         <v>104174</v>
@@ -1921,7 +1990,7 @@
         <v>0.38775862068965522</v>
       </c>
       <c r="M28" s="5">
-        <v>0.98145454545454536</v>
+        <v>0.97033898305084743</v>
       </c>
       <c r="N28" s="3">
         <v>192</v>
@@ -1929,35 +1998,35 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C29" s="3">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D29" s="4">
-        <v>270523</v>
+        <v>263638</v>
       </c>
       <c r="E29" s="3">
-        <v>116</v>
+        <v>189</v>
       </c>
       <c r="F29" s="4">
-        <v>158415</v>
+        <v>253234</v>
       </c>
       <c r="G29" s="3">
         <v>124744</v>
       </c>
       <c r="H29" s="3">
-        <v>10137</v>
+        <v>10138</v>
       </c>
       <c r="I29" s="3">
         <v>784</v>
       </c>
       <c r="J29" s="5">
         <f t="shared" si="0"/>
-        <v>8.12624254473161E-2</v>
+        <v>8.1270441864939397E-2</v>
       </c>
       <c r="K29" s="5">
         <v>0.1098958333333333</v>
@@ -1966,7 +2035,7 @@
         <v>0.4292537313432836</v>
       </c>
       <c r="M29" s="5">
-        <v>0.96081632653061222</v>
+        <v>0.96196969696969703</v>
       </c>
       <c r="N29" s="3">
         <v>241</v>
@@ -1974,70 +2043,70 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="C30" s="3">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D30" s="4">
-        <v>209700</v>
+        <v>202823</v>
       </c>
       <c r="E30" s="3">
-        <v>63</v>
+        <v>159</v>
       </c>
       <c r="F30" s="4">
-        <v>84203</v>
+        <v>201923</v>
       </c>
       <c r="G30" s="3">
         <v>116090</v>
       </c>
       <c r="H30" s="3">
-        <v>8907</v>
+        <v>8909</v>
       </c>
       <c r="I30" s="3">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="J30" s="5">
         <f t="shared" si="0"/>
-        <v>7.6724954776466528E-2</v>
+        <v>7.6742182789215269E-2</v>
       </c>
       <c r="K30" s="5">
         <v>9.9666666666666667E-2</v>
       </c>
       <c r="L30" s="5">
-        <v>0.3960377358490566</v>
+        <v>0.39584905660377362</v>
       </c>
       <c r="M30" s="5">
-        <v>0.99624999999999997</v>
+        <v>0.9812727272727273</v>
       </c>
       <c r="N30" s="3">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C31" s="3">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="D31" s="4">
-        <v>264099</v>
+        <v>246041</v>
       </c>
       <c r="E31" s="3">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="F31" s="4">
-        <v>35929</v>
+        <v>232074</v>
       </c>
       <c r="G31" s="3">
-        <v>154035</v>
+        <v>178027</v>
       </c>
       <c r="H31" s="3">
         <v>10262</v>
@@ -2047,7 +2116,7 @@
       </c>
       <c r="J31" s="5">
         <f t="shared" si="0"/>
-        <v>6.662122244944331E-2</v>
+        <v>5.7642941800962778E-2</v>
       </c>
       <c r="K31" s="5">
         <v>9.3092783505154653E-2</v>
@@ -2056,7 +2125,7 @@
         <v>0.43463768115942031</v>
       </c>
       <c r="M31" s="5">
-        <v>1</v>
+        <v>0.95388059701492534</v>
       </c>
       <c r="N31" s="3">
         <v>276</v>
@@ -2067,48 +2136,723 @@
         <v>68</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C32" s="3">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="D32" s="4">
-        <v>246278</v>
+        <v>231373</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="F32" s="4">
-        <v>0</v>
+        <v>216974</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>133695</v>
       </c>
       <c r="H32" s="3">
-        <v>9530</v>
+        <v>9535</v>
       </c>
       <c r="I32" s="3">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="J32" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.1319047084782525E-2</v>
       </c>
       <c r="K32" s="5">
-        <v>9.4574468085106389E-2</v>
+        <v>9.4680851063829785E-2</v>
       </c>
       <c r="L32" s="5">
-        <v>0.46822580645161288</v>
+        <v>0.46857142857142853</v>
       </c>
       <c r="M32" s="5">
-        <v>0</v>
+        <v>0.94920634920634928</v>
       </c>
       <c r="N32" s="3">
         <v>264</v>
       </c>
     </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="3">
+        <v>230</v>
+      </c>
+      <c r="D33" s="4">
+        <v>298962</v>
+      </c>
+      <c r="E33" s="3">
+        <v>214</v>
+      </c>
+      <c r="F33" s="4">
+        <v>278501</v>
+      </c>
+      <c r="G33" s="3">
+        <v>109417</v>
+      </c>
+      <c r="H33" s="3">
+        <v>9637</v>
+      </c>
+      <c r="I33" s="3">
+        <v>799</v>
+      </c>
+      <c r="J33" s="5">
+        <f t="shared" si="0"/>
+        <v>8.8075893142747469E-2</v>
+      </c>
+      <c r="K33" s="5">
+        <v>9.5416666666666664E-2</v>
+      </c>
+      <c r="L33" s="5">
+        <v>0.45720588235294118</v>
+      </c>
+      <c r="M33" s="5">
+        <v>0.95940298507462685</v>
+      </c>
+      <c r="N33" s="3">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="3">
+        <v>199</v>
+      </c>
+      <c r="D34" s="4">
+        <v>237303</v>
+      </c>
+      <c r="E34" s="3">
+        <v>183</v>
+      </c>
+      <c r="F34" s="4">
+        <v>220260</v>
+      </c>
+      <c r="G34" s="3">
+        <v>118194</v>
+      </c>
+      <c r="H34" s="3">
+        <v>9686</v>
+      </c>
+      <c r="I34" s="3">
+        <v>834</v>
+      </c>
+      <c r="J34" s="5">
+        <f t="shared" si="0"/>
+        <v>8.1950014383132819E-2</v>
+      </c>
+      <c r="K34" s="5">
+        <v>8.4021739130434786E-2</v>
+      </c>
+      <c r="L34" s="5">
+        <v>0.42114754098360663</v>
+      </c>
+      <c r="M34" s="5">
+        <v>0.96750000000000003</v>
+      </c>
+      <c r="N34" s="3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="3">
+        <v>202</v>
+      </c>
+      <c r="D35" s="4">
+        <v>246841</v>
+      </c>
+      <c r="E35" s="3">
+        <v>183</v>
+      </c>
+      <c r="F35" s="4">
+        <v>221735</v>
+      </c>
+      <c r="G35" s="3">
+        <v>125869</v>
+      </c>
+      <c r="H35" s="3">
+        <v>9777</v>
+      </c>
+      <c r="I35" s="3">
+        <v>825</v>
+      </c>
+      <c r="J35" s="5">
+        <f t="shared" si="0"/>
+        <v>7.7675996472523018E-2</v>
+      </c>
+      <c r="K35" s="5">
+        <v>9.1145833333333343E-2</v>
+      </c>
+      <c r="L35" s="5">
+        <v>0.40693548387096778</v>
+      </c>
+      <c r="M35" s="5">
+        <v>0.96830508474576282</v>
+      </c>
+      <c r="N35" s="3">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="3">
+        <v>217</v>
+      </c>
+      <c r="D36" s="4">
+        <v>263169</v>
+      </c>
+      <c r="E36" s="3">
+        <v>196</v>
+      </c>
+      <c r="F36" s="4">
+        <v>238382</v>
+      </c>
+      <c r="G36" s="3">
+        <v>151601</v>
+      </c>
+      <c r="H36" s="3">
+        <v>11714</v>
+      </c>
+      <c r="I36" s="3">
+        <v>876</v>
+      </c>
+      <c r="J36" s="5">
+        <f t="shared" si="0"/>
+        <v>7.7268619600134564E-2</v>
+      </c>
+      <c r="K36" s="5">
+        <v>8.9361702127659565E-2</v>
+      </c>
+      <c r="L36" s="5">
+        <v>0.39724137931034492</v>
+      </c>
+      <c r="M36" s="5">
+        <v>0.9754385964912281</v>
+      </c>
+      <c r="N36" s="3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="3">
+        <v>190</v>
+      </c>
+      <c r="D37" s="4">
+        <v>232058</v>
+      </c>
+      <c r="E37" s="3">
+        <v>171</v>
+      </c>
+      <c r="F37" s="4">
+        <v>208955</v>
+      </c>
+      <c r="G37" s="3">
+        <v>125659</v>
+      </c>
+      <c r="H37" s="3">
+        <v>9049</v>
+      </c>
+      <c r="I37" s="3">
+        <v>687</v>
+      </c>
+      <c r="J37" s="5">
+        <f t="shared" si="0"/>
+        <v>7.2012350886128326E-2</v>
+      </c>
+      <c r="K37" s="5">
+        <v>9.6372549019607845E-2</v>
+      </c>
+      <c r="L37" s="5">
+        <v>0.48380281690140847</v>
+      </c>
+      <c r="M37" s="5">
+        <v>0.96705882352941175</v>
+      </c>
+      <c r="N37" s="3">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="3">
+        <v>182</v>
+      </c>
+      <c r="D38" s="4">
+        <v>225241</v>
+      </c>
+      <c r="E38" s="3">
+        <v>168</v>
+      </c>
+      <c r="F38" s="4">
+        <v>208003</v>
+      </c>
+      <c r="G38" s="3">
+        <v>127638</v>
+      </c>
+      <c r="H38" s="3">
+        <v>8766</v>
+      </c>
+      <c r="I38" s="3">
+        <v>687</v>
+      </c>
+      <c r="J38" s="5">
+        <f t="shared" si="0"/>
+        <v>6.8678606684529686E-2</v>
+      </c>
+      <c r="K38" s="5">
+        <v>9.4111111111111118E-2</v>
+      </c>
+      <c r="L38" s="5">
+        <v>0.44210526315789472</v>
+      </c>
+      <c r="M38" s="5">
+        <v>0.95627450980392159</v>
+      </c>
+      <c r="N38" s="3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="3">
+        <v>210</v>
+      </c>
+      <c r="D39" s="4">
+        <v>264707</v>
+      </c>
+      <c r="E39" s="3">
+        <v>174</v>
+      </c>
+      <c r="F39" s="4">
+        <v>216771</v>
+      </c>
+      <c r="G39" s="3">
+        <v>106293</v>
+      </c>
+      <c r="H39" s="3">
+        <v>9322</v>
+      </c>
+      <c r="I39" s="3">
+        <v>733</v>
+      </c>
+      <c r="J39" s="5">
+        <f t="shared" si="0"/>
+        <v>8.77009774867583E-2</v>
+      </c>
+      <c r="K39" s="5">
+        <v>8.8229166666666664E-2</v>
+      </c>
+      <c r="L39" s="5">
+        <v>0.44355932203389842</v>
+      </c>
+      <c r="M39" s="5">
+        <v>0.96660377358490568</v>
+      </c>
+      <c r="N39" s="3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="3">
+        <v>202</v>
+      </c>
+      <c r="D40" s="4">
+        <v>256249</v>
+      </c>
+      <c r="E40" s="3">
+        <v>162</v>
+      </c>
+      <c r="F40" s="4">
+        <v>204051</v>
+      </c>
+      <c r="G40" s="3">
+        <v>118351</v>
+      </c>
+      <c r="H40" s="3">
+        <v>10067</v>
+      </c>
+      <c r="I40" s="3">
+        <v>836</v>
+      </c>
+      <c r="J40" s="5">
+        <f t="shared" si="0"/>
+        <v>8.5060540257370032E-2</v>
+      </c>
+      <c r="K40" s="5">
+        <v>0.1154838709677419</v>
+      </c>
+      <c r="L40" s="5">
+        <v>0.45411764705882363</v>
+      </c>
+      <c r="M40" s="5">
+        <v>0.96030303030303032</v>
+      </c>
+      <c r="N40" s="3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="3">
+        <v>218</v>
+      </c>
+      <c r="D41" s="4">
+        <v>269392</v>
+      </c>
+      <c r="E41" s="3">
+        <v>175</v>
+      </c>
+      <c r="F41" s="4">
+        <v>213155</v>
+      </c>
+      <c r="G41" s="3">
+        <v>121351</v>
+      </c>
+      <c r="H41" s="3">
+        <v>9773</v>
+      </c>
+      <c r="I41" s="3">
+        <v>821</v>
+      </c>
+      <c r="J41" s="5">
+        <f t="shared" si="0"/>
+        <v>8.0534977050044906E-2</v>
+      </c>
+      <c r="K41" s="5">
+        <v>9.4883720930232562E-2</v>
+      </c>
+      <c r="L41" s="5">
+        <v>0.44967741935483868</v>
+      </c>
+      <c r="M41" s="5">
+        <v>0.96727272727272728</v>
+      </c>
+      <c r="N41" s="3">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="3">
+        <v>236</v>
+      </c>
+      <c r="D42" s="4">
+        <v>287889</v>
+      </c>
+      <c r="E42" s="3">
+        <v>168</v>
+      </c>
+      <c r="F42" s="4">
+        <v>207954</v>
+      </c>
+      <c r="G42" s="3">
+        <v>118383</v>
+      </c>
+      <c r="H42" s="3">
+        <v>10391</v>
+      </c>
+      <c r="I42" s="3">
+        <v>894</v>
+      </c>
+      <c r="J42" s="5">
+        <f t="shared" si="0"/>
+        <v>8.7774427071454511E-2</v>
+      </c>
+      <c r="K42" s="5">
+        <v>0.1240909090909091</v>
+      </c>
+      <c r="L42" s="5">
+        <v>0.39475409836065573</v>
+      </c>
+      <c r="M42" s="5">
+        <v>0.98226415094339625</v>
+      </c>
+      <c r="N42" s="3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="3">
+        <v>203</v>
+      </c>
+      <c r="D43" s="4">
+        <v>239990</v>
+      </c>
+      <c r="E43" s="3">
+        <v>142</v>
+      </c>
+      <c r="F43" s="4">
+        <v>163569</v>
+      </c>
+      <c r="G43" s="3">
+        <v>132474</v>
+      </c>
+      <c r="H43" s="3">
+        <v>10105</v>
+      </c>
+      <c r="I43" s="3">
+        <v>900</v>
+      </c>
+      <c r="J43" s="5">
+        <f t="shared" si="0"/>
+        <v>7.6279118921448744E-2</v>
+      </c>
+      <c r="K43" s="5">
+        <v>8.91566265060241E-2</v>
+      </c>
+      <c r="L43" s="5">
+        <v>0.45491525423728818</v>
+      </c>
+      <c r="M43" s="5">
+        <v>0.98</v>
+      </c>
+      <c r="N43" s="3">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="3">
+        <v>205</v>
+      </c>
+      <c r="D44" s="4">
+        <v>252771</v>
+      </c>
+      <c r="E44" s="3">
+        <v>127</v>
+      </c>
+      <c r="F44" s="4">
+        <v>152475</v>
+      </c>
+      <c r="G44" s="3">
+        <v>132050</v>
+      </c>
+      <c r="H44" s="3">
+        <v>9968</v>
+      </c>
+      <c r="I44" s="3">
+        <v>812</v>
+      </c>
+      <c r="J44" s="5">
+        <f t="shared" si="0"/>
+        <v>7.5486558121923508E-2</v>
+      </c>
+      <c r="K44" s="5">
+        <v>9.6382978723404247E-2</v>
+      </c>
+      <c r="L44" s="5">
+        <v>0.51819672131147543</v>
+      </c>
+      <c r="M44" s="5">
+        <v>0.99260000000000004</v>
+      </c>
+      <c r="N44" s="3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" s="3">
+        <v>199</v>
+      </c>
+      <c r="D45" s="4">
+        <v>252424</v>
+      </c>
+      <c r="E45" s="3">
+        <v>64</v>
+      </c>
+      <c r="F45" s="4">
+        <v>73842</v>
+      </c>
+      <c r="G45" s="3">
+        <v>114216</v>
+      </c>
+      <c r="H45" s="3">
+        <v>8977</v>
+      </c>
+      <c r="I45" s="3">
+        <v>754</v>
+      </c>
+      <c r="J45" s="5">
+        <f t="shared" si="0"/>
+        <v>7.8596693983329829E-2</v>
+      </c>
+      <c r="K45" s="5">
+        <v>0.10102272727272731</v>
+      </c>
+      <c r="L45" s="5">
+        <v>0.45468750000000002</v>
+      </c>
+      <c r="M45" s="5">
+        <v>0.99051282051282064</v>
+      </c>
+      <c r="N45" s="3">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" s="3">
+        <v>265</v>
+      </c>
+      <c r="D46" s="4">
+        <v>330425</v>
+      </c>
+      <c r="E46" s="3">
+        <v>25</v>
+      </c>
+      <c r="F46" s="4">
+        <v>37560</v>
+      </c>
+      <c r="G46" s="3">
+        <v>121481</v>
+      </c>
+      <c r="H46" s="3">
+        <v>10094</v>
+      </c>
+      <c r="I46" s="3">
+        <v>859</v>
+      </c>
+      <c r="J46" s="5">
+        <f t="shared" si="0"/>
+        <v>8.3091182983347195E-2</v>
+      </c>
+      <c r="K46" s="5">
+        <v>9.8275862068965519E-2</v>
+      </c>
+      <c r="L46" s="5">
+        <v>0.47347826086956518</v>
+      </c>
+      <c r="M46" s="5">
+        <v>1</v>
+      </c>
+      <c r="N46" s="3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="3">
+        <v>209</v>
+      </c>
+      <c r="D47" s="4">
+        <v>264208</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>118256</v>
+      </c>
+      <c r="H47" s="3">
+        <v>9584</v>
+      </c>
+      <c r="I47" s="3">
+        <v>766</v>
+      </c>
+      <c r="J47" s="5">
+        <f t="shared" si="0"/>
+        <v>8.1044513597618731E-2</v>
+      </c>
+      <c r="K47" s="5">
+        <v>9.3375E-2</v>
+      </c>
+      <c r="L47" s="5">
+        <v>0.43606557377049182</v>
+      </c>
+      <c r="M47" s="5">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>273</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C3:C32">
+  <conditionalFormatting sqref="C3:D47">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>C3&gt;C2</formula>
     </cfRule>
@@ -2116,19 +2860,19 @@
       <formula>C3&lt;C2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G32">
-    <cfRule type="expression" dxfId="3" priority="3">
+  <conditionalFormatting sqref="G3:G47">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>G3&gt;G2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>G3&lt;G2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:L32">
-    <cfRule type="expression" dxfId="1" priority="5">
+  <conditionalFormatting sqref="I3:L47">
+    <cfRule type="expression" dxfId="1" priority="7">
       <formula>I3&gt;I2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>I3&lt;I2</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Ежедневная статистика.xlsx
+++ b/Ежедневная статистика.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.7109375" customWidth="1" min="1" max="1"/>
@@ -1671,7 +1671,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>02.04.2026 10:53</t>
+          <t>17.04.2026 17:28</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1680,16 +1680,16 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>244036</v>
+        <v>236208</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>228774</v>
+        <v>234859</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>145959</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.114020618556701</v>
+        <v>0.1138497943586379</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.4131746031746031</v>
+        <v>0.3860207036608719</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>0.9551724137931035</v>
+        <v>0.9991079393398752</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>268</v>
@@ -1720,7 +1720,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>02.04.2026 10:54</t>
+          <t>17.04.2026 17:28</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1729,16 +1729,16 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>236892</v>
+        <v>229611</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>217864</v>
+        <v>228071</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>120611</v>
@@ -1754,13 +1754,13 @@
         <v/>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0.09440860215053765</v>
+        <v>0.09414799010456781</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.4245</v>
+        <v>0.4181047143263371</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.9842105263157894</v>
+        <v>0.9966101694915254</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>271</v>
@@ -1769,7 +1769,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02.04.2026 10:55</t>
+          <t>17.04.2026 17:28</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1778,16 +1778,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>201511</v>
+        <v>190321</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>179934</v>
+        <v>188768</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>120093</v>
@@ -1803,22 +1803,22 @@
         <v/>
       </c>
       <c r="K27" s="5" t="n">
-        <v>0.105</v>
+        <v>0.1043551647071151</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0.4106896551724138</v>
+        <v>0.4003146231585319</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>0.9501851851851852</v>
+        <v>0.9940476190476191</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02.04.2026 10:55</t>
+          <t>17.04.2026 17:29</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1827,16 +1827,16 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>243859</v>
+        <v>241560</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>231958</v>
+        <v>240660</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>104174</v>
@@ -1852,13 +1852,13 @@
         <v/>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.09926829268292683</v>
+        <v>0.09920619843555986</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.3877586206896552</v>
+        <v>0.3760151148041919</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.9703389830508474</v>
+        <v>0.9959016393442623</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>192</v>
@@ -1867,7 +1867,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>07.04.2026 09:40</t>
+          <t>17.04.2026 17:29</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1876,16 +1876,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>263638</v>
+        <v>259591</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>253234</v>
+        <v>255162</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>124744</v>
@@ -1901,13 +1901,13 @@
         <v/>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0.1098958333333333</v>
+        <v>0.1094768570081052</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.4292537313432836</v>
+        <v>0.4208369716359194</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>0.961969696969697</v>
+        <v>0.9930348258706467</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>241</v>
@@ -1916,7 +1916,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>08.04.2026 11:25</t>
+          <t>17.04.2026 17:29</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1931,10 +1931,10 @@
         <v>202823</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>201923</v>
+        <v>202823</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>116090</v>
@@ -1950,13 +1950,13 @@
         <v/>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.09966666666666667</v>
+        <v>0.09932830024576353</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.3958490566037736</v>
+        <v>0.3833079386960956</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.9812727272727273</v>
+        <v>1</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>269</v>
@@ -1965,7 +1965,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>08.04.2026 07:23</t>
+          <t>17.04.2026 17:30</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1974,16 +1974,16 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>246041</v>
+        <v>237975</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>232074</v>
+        <v>236309</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>178027</v>
@@ -1999,13 +1999,13 @@
         <v/>
       </c>
       <c r="K31" s="5" t="n">
-        <v>0.09309278350515465</v>
+        <v>0.09256115559653524</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.4346376811594203</v>
+        <v>0.4168230396944429</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>0.9538805970149253</v>
+        <v>0.9926470588235294</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>276</v>
@@ -2014,7 +2014,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>10.04.2026 06:54</t>
+          <t>17.04.2026 17:30</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2023,16 +2023,16 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>231373</v>
+        <v>222254</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>216974</v>
+        <v>220255</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>133695</v>
@@ -2048,22 +2048,22 @@
         <v/>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0.09468085106382979</v>
+        <v>0.09523995936544892</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.4685714285714285</v>
+        <v>0.4412772048991352</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>0.9492063492063493</v>
+        <v>0.9894179894179895</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>10.04.2026 06:55</t>
+          <t>17.04.2026 17:30</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2072,16 +2072,16 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>298962</v>
+        <v>290463</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>278501</v>
+        <v>283465</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>109417</v>
@@ -2097,13 +2097,13 @@
         <v/>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.09541666666666666</v>
+        <v>0.09554601321789453</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.4572058823529412</v>
+        <v>0.4318796704530512</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>0.9594029850746268</v>
+        <v>0.9890547263681592</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>284</v>
@@ -2112,7 +2112,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10.04.2026 06:56</t>
+          <t>17.04.2026 17:31</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2121,16 +2121,16 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>237303</v>
+        <v>228560</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>220260</v>
+        <v>226467</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>118194</v>
@@ -2146,13 +2146,13 @@
         <v/>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0.08402173913043479</v>
+        <v>0.0832398636711368</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.4211475409836066</v>
+        <v>0.3778643081566087</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.9675</v>
+        <v>0.9904371584699454</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>212</v>
@@ -2161,7 +2161,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>13.04.2026 11:07</t>
+          <t>17.04.2026 17:31</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2170,16 +2170,16 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>244495</v>
+        <v>242999</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>235999</v>
+        <v>238800</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>125869</v>
@@ -2195,13 +2195,13 @@
         <v/>
       </c>
       <c r="K35" s="5" t="n">
-        <v>0.09114583333333334</v>
+        <v>0.09100096150006061</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.4069354838709678</v>
+        <v>0.3953336264404388</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>0.966</v>
+        <v>0.9895833333333333</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>262</v>
@@ -2210,7 +2210,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>14.04.2026 12:18</t>
+          <t>17.04.2026 17:32</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2219,16 +2219,16 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>263169</v>
+        <v>260823</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>250640</v>
+        <v>252136</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>151601</v>
@@ -2244,22 +2244,22 @@
         <v/>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0.08936170212765956</v>
+        <v>0.08913498755894793</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.3972413793103449</v>
+        <v>0.3888521028207311</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>0.9765517241379311</v>
+        <v>0.9700564971751412</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>15.04.2026 13:59</t>
+          <t>17.04.2026 09:50</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2268,16 +2268,16 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>229678</v>
+        <v>228828</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>224557</v>
+        <v>226053</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>125659</v>
@@ -2299,7 +2299,7 @@
         <v>0.4838028169014085</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>0.9643661971830986</v>
+        <v>0.9597183098591549</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>253</v>
@@ -2308,7 +2308,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15.04.2026 14:02</t>
+          <t>17.04.2026 17:32</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2323,10 +2323,10 @@
         <v>222601</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>220005</v>
+        <v>221780</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>127638</v>
@@ -2342,13 +2342,13 @@
         <v/>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0.09411111111111112</v>
+        <v>0.09353832401175154</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.4421052631578947</v>
+        <v>0.4146882641400185</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.9562264150943396</v>
+        <v>0.9969696969696968</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>250</v>
@@ -2357,7 +2357,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15.04.2026 14:03</t>
+          <t>17.04.2026 17:33</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2366,16 +2366,16 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>255568</v>
+        <v>254248</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>243342</v>
+        <v>247004</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>106293</v>
@@ -2391,13 +2391,13 @@
         <v/>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0.08822916666666666</v>
+        <v>0.08766490778139797</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.4435593220338984</v>
+        <v>0.4107605732433732</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>0.9553571428571429</v>
+        <v>0.9745196324143692</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>225</v>
@@ -2406,7 +2406,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>13.04.2026 11:10</t>
+          <t>17.04.2026 17:33</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2421,10 +2421,10 @@
         <v>252774</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>238283</v>
+        <v>239603</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>118351</v>
@@ -2440,13 +2440,13 @@
         <v/>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0.1154838709677419</v>
+        <v>0.1154459723294125</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.4541176470588236</v>
+        <v>0.433924838000625</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.9519117647058823</v>
+        <v>0.9645424836601307</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>268</v>
@@ -2455,7 +2455,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>15.04.2026 14:04</t>
+          <t>17.04.2026 17:33</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2464,16 +2464,16 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>265447</v>
+        <v>264627</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>247714</v>
+        <v>250564</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>121351</v>
@@ -2489,13 +2489,13 @@
         <v/>
       </c>
       <c r="K41" s="5" t="n">
-        <v>0.09488372093023256</v>
+        <v>0.09464708685355</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.4496774193548387</v>
+        <v>0.4202524504641708</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>0.9633333333333333</v>
+        <v>0.9768939393939394</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>242</v>
@@ -2504,7 +2504,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>15.04.2026 14:05</t>
+          <t>17.04.2026 17:34</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2519,10 +2519,10 @@
         <v>284304</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>265149</v>
+        <v>277252</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>118383</v>
@@ -2538,22 +2538,22 @@
         <v/>
       </c>
       <c r="K42" s="5" t="n">
-        <v>0.1240909090909091</v>
+        <v>0.1240417093052043</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0.3947540983606557</v>
+        <v>0.3749423298380241</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>0.9770175438596492</v>
+        <v>0.9827586206896552</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>15.04.2026 14:05</t>
+          <t>17.04.2026 17:34</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2568,10 +2568,10 @@
         <v>239990</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>222772</v>
+        <v>227940</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>132474</v>
@@ -2587,13 +2587,13 @@
         <v/>
       </c>
       <c r="K43" s="5" t="n">
-        <v>0.0891566265060241</v>
+        <v>0.08919192295384132</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>0.4549152542372882</v>
+        <v>0.4498856959644273</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>0.9872131147540983</v>
+        <v>0.9539422326307573</v>
       </c>
       <c r="N43" s="3" t="n">
         <v>244</v>
@@ -2602,7 +2602,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>15.04.2026 14:06</t>
+          <t>17.04.2026 17:34</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>245814</v>
+        <v>244174</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>218652</v>
+        <v>230972</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>132050</v>
@@ -2636,13 +2636,13 @@
         <v/>
       </c>
       <c r="K44" s="5" t="n">
-        <v>0.09638297872340425</v>
+        <v>0.09613466699530962</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0.5181967213114754</v>
+        <v>0.5008679854553937</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0.9849122807017544</v>
+        <v>0.9903393541324577</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>290</v>
@@ -2651,7 +2651,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>15.04.2026 14:07</t>
+          <t>17.04.2026 17:35</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2660,16 +2660,16 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>243508</v>
+        <v>242203</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>205945</v>
+        <v>217369</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>114216</v>
@@ -2685,13 +2685,13 @@
         <v/>
       </c>
       <c r="K45" s="5" t="n">
-        <v>0.1010227272727273</v>
+        <v>0.1013203344883969</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.4546875</v>
+        <v>0.4467041427770604</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>0.9688135593220339</v>
+        <v>0.9395792505036202</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>245</v>
@@ -2700,7 +2700,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>15.04.2026 14:07</t>
+          <t>17.04.2026 17:35</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2709,16 +2709,16 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>321154</v>
+        <v>320304</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>269902</v>
+        <v>285676</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>121481</v>
@@ -2734,13 +2734,13 @@
         <v/>
       </c>
       <c r="K46" s="5" t="n">
-        <v>0.09827586206896552</v>
+        <v>0.09797670833137286</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>0.4734782608695652</v>
+        <v>0.4609422646259695</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>0.9594202898550726</v>
+        <v>0.9418439048873831</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>259</v>
@@ -2749,7 +2749,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>15.04.2026 14:08</t>
+          <t>17.04.2026 17:35</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2758,16 +2758,16 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>258298</v>
+        <v>256978</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>197454</v>
+        <v>221295</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>119829</v>
@@ -2783,13 +2783,13 @@
         <v/>
       </c>
       <c r="K47" s="5" t="n">
-        <v>0.0935</v>
+        <v>0.0934337198845593</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>0.4354098360655738</v>
+        <v>0.4234409828599891</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>0.9835714285714287</v>
+        <v>0.9254116222760289</v>
       </c>
       <c r="N47" s="3" t="n">
         <v>276</v>
@@ -2798,7 +2798,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15.04.2026 14:08</t>
+          <t>17.04.2026 17:36</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2807,16 +2807,16 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>231107</v>
+        <v>229157</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>168120</v>
+        <v>193018</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>116186</v>
@@ -2832,13 +2832,13 @@
         <v/>
       </c>
       <c r="K48" s="5" t="n">
-        <v>0.09402173913043478</v>
+        <v>0.09332617958747337</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>0.4371428571428572</v>
+        <v>0.4312805542578978</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>0.9910344827586206</v>
+        <v>0.8975800612642719</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>221</v>
@@ -2847,7 +2847,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15.04.2026 14:09</t>
+          <t>17.04.2026 17:36</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2856,22 +2856,22 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>266444</v>
+        <v>262284</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>159091</v>
+        <v>192807</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>132670</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>9268</v>
+        <v>9269</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>837</v>
@@ -2881,22 +2881,22 @@
         <v/>
       </c>
       <c r="K49" s="5" t="n">
-        <v>0.1319565217391304</v>
+        <v>0.132058058168728</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>0.4208823529411764</v>
+        <v>0.4170821090433728</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>0.9824561403508772</v>
+        <v>0.8354197714853453</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>15.04.2026 14:10</t>
+          <t>17.04.2026 17:36</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2905,22 +2905,22 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>278682</v>
+        <v>275094</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>98</v>
+        <v>163</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>127980</v>
+        <v>209048</v>
       </c>
       <c r="G50" s="3" t="n">
         <v>137381</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>10012</v>
+        <v>10013</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>814</v>
@@ -2930,13 +2930,13 @@
         <v/>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0.1076666666666667</v>
+        <v>0.1074529622189541</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>0.468955223880597</v>
+        <v>0.4659879137463322</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.9808333333333333</v>
+        <v>0.836602418745276</v>
       </c>
       <c r="N50" s="3" t="n">
         <v>344</v>
@@ -2945,7 +2945,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>15.04.2026 14:10</t>
+          <t>17.04.2026 17:37</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2954,22 +2954,22 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>279557</v>
+        <v>269804</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>65119</v>
+        <v>173763</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>9129</v>
+        <v>9148</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>782</v>
@@ -2979,13 +2979,13 @@
         <v/>
       </c>
       <c r="K51" s="5" t="n">
-        <v>0.1194845360824742</v>
+        <v>0.1192509918940285</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>0.4537878787878787</v>
+        <v>0.4522169832354956</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>1</v>
+        <v>0.7390394088669952</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>286</v>
@@ -2994,7 +2994,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>15.04.2026 14:11</t>
+          <t>17.04.2026 17:37</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3003,45 +3003,143 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>301968</v>
+        <v>298298</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>10685</v>
+        <v>139398</v>
       </c>
       <c r="G52" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>9523</v>
+        <v>9527</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="J52" s="5">
         <f>IFERROR(H52/G52,0)</f>
         <v/>
       </c>
       <c r="K52" s="5" t="n">
-        <v>0.1101123595505618</v>
+        <v>0.1094922066310599</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>0.419375</v>
+        <v>0.41741353115254</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>1</v>
+        <v>0.6452679843304844</v>
       </c>
       <c r="N52" s="3" t="n">
         <v>228</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>17.04.2026 17:38</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>15.04.2026</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>228</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>278172</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>71480</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>10794</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>852</v>
+      </c>
+      <c r="J53" s="5">
+        <f>IFERROR(H53/G53,0)</f>
+        <v/>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0.09434239813575719</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>0.4183435410764507</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>0.4182166199813259</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>17.04.2026 17:38</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>16.04.2026</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>374933</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>10982</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>11059</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>998</v>
+      </c>
+      <c r="J54" s="5">
+        <f>IFERROR(H54/G54,0)</f>
+        <v/>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0.09236646921504635</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0.4422658379778256</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0.3523809523809524</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>222</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C3:C52">
+  <conditionalFormatting sqref="C3:C54">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>C3&gt;C2</formula>
     </cfRule>
@@ -3049,7 +3147,7 @@
       <formula>C3&lt;C2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:D52">
+  <conditionalFormatting sqref="D3:D54">
     <cfRule type="expression" priority="3" dxfId="0">
       <formula>D3&gt;D2</formula>
     </cfRule>
@@ -3057,7 +3155,7 @@
       <formula>D3&lt;D2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G52">
+  <conditionalFormatting sqref="G3:G54">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>G3&gt;G2</formula>
     </cfRule>
@@ -3065,7 +3163,7 @@
       <formula>G3&lt;G2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I52">
+  <conditionalFormatting sqref="I3:I54">
     <cfRule type="expression" priority="7" dxfId="0">
       <formula>I3&gt;I2</formula>
     </cfRule>
@@ -3073,7 +3171,7 @@
       <formula>I3&lt;I2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3:J52">
+  <conditionalFormatting sqref="J3:J54">
     <cfRule type="expression" priority="9" dxfId="0">
       <formula>J3&gt;J2</formula>
     </cfRule>
@@ -3081,7 +3179,7 @@
       <formula>J3&lt;J2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K52">
+  <conditionalFormatting sqref="K3:K54">
     <cfRule type="expression" priority="11" dxfId="0">
       <formula>K3&gt;K2</formula>
     </cfRule>
@@ -3089,7 +3187,7 @@
       <formula>K3&lt;K2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L52">
+  <conditionalFormatting sqref="L3:L54">
     <cfRule type="expression" priority="13" dxfId="0">
       <formula>L3&gt;L2</formula>
     </cfRule>

--- a/Ежедневная статистика.xlsx
+++ b/Ежедневная статистика.xlsx
@@ -8,22 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dergacevad\Folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5B194D-6A52-4DC5-AC5E-D20E539CBD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B767F63C-D915-46F2-A630-92ED050EE5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Статистика" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Статистика!$A$1:$N$381</definedName>
-  </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="558">
   <si>
     <t>Обновлено</t>
   </si>
@@ -1573,6 +1570,9 @@
     <t>13.04.2026</t>
   </si>
   <si>
+    <t>13.05.2026 17:04</t>
+  </si>
+  <si>
     <t>14.04.2026</t>
   </si>
   <si>
@@ -1582,13 +1582,16 @@
     <t>15.04.2026</t>
   </si>
   <si>
+    <t>13.05.2026 17:05</t>
+  </si>
+  <si>
     <t>16.04.2026</t>
   </si>
   <si>
     <t>17.04.2026</t>
   </si>
   <si>
-    <t>06.05.2026 15:36</t>
+    <t>13.05.2026 17:06</t>
   </si>
   <si>
     <t>18.04.2026</t>
@@ -1597,40 +1600,40 @@
     <t>19.04.2026</t>
   </si>
   <si>
-    <t>06.05.2026 15:37</t>
-  </si>
-  <si>
     <t>20.04.2026</t>
   </si>
   <si>
+    <t>13.05.2026 17:07</t>
+  </si>
+  <si>
     <t>21.04.2026</t>
   </si>
   <si>
+    <t>13.05.2026 16:53</t>
+  </si>
+  <si>
     <t>22.04.2026</t>
   </si>
   <si>
-    <t>06.05.2026 15:38</t>
-  </si>
-  <si>
     <t>23.04.2026</t>
   </si>
   <si>
     <t>24.04.2026</t>
   </si>
   <si>
+    <t>13.05.2026 16:54</t>
+  </si>
+  <si>
     <t>25.04.2026</t>
   </si>
   <si>
-    <t>06.05.2026 15:39</t>
-  </si>
-  <si>
     <t>26.04.2026</t>
   </si>
   <si>
     <t>27.04.2026</t>
   </si>
   <si>
-    <t>06.05.2026 15:40</t>
+    <t>13.05.2026 16:55</t>
   </si>
   <si>
     <t>28.04.2026</t>
@@ -1642,7 +1645,7 @@
     <t>30.04.2026</t>
   </si>
   <si>
-    <t>06.05.2026 15:41</t>
+    <t>13.05.2026 16:56</t>
   </si>
   <si>
     <t>01.05.2026</t>
@@ -1651,16 +1654,46 @@
     <t>02.05.2026</t>
   </si>
   <si>
+    <t>13.05.2026 16:57</t>
+  </si>
+  <si>
     <t>03.05.2026</t>
   </si>
   <si>
-    <t>06.05.2026 15:42</t>
-  </si>
-  <si>
     <t>04.05.2026</t>
   </si>
   <si>
     <t>05.05.2026</t>
+  </si>
+  <si>
+    <t>13.05.2026 16:58</t>
+  </si>
+  <si>
+    <t>06.05.2026</t>
+  </si>
+  <si>
+    <t>07.05.2026</t>
+  </si>
+  <si>
+    <t>08.05.2026</t>
+  </si>
+  <si>
+    <t>13.05.2026 16:59</t>
+  </si>
+  <si>
+    <t>09.05.2026</t>
+  </si>
+  <si>
+    <t>10.05.2026</t>
+  </si>
+  <si>
+    <t>11.05.2026</t>
+  </si>
+  <si>
+    <t>13.05.2026 17:00</t>
+  </si>
+  <si>
+    <t>12.05.2026</t>
   </si>
 </sst>
 </file>
@@ -2079,7 +2112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N381"/>
+  <dimension ref="A1:N388"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -8145,7 +8178,7 @@
         <v>148933</v>
       </c>
       <c r="G135" s="3">
-        <v>0</v>
+        <v>128078</v>
       </c>
       <c r="H135" s="3">
         <v>8967</v>
@@ -8155,7 +8188,7 @@
       </c>
       <c r="J135" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.0012023922921968E-2</v>
       </c>
       <c r="K135" s="5">
         <v>7.821463758302595E-2</v>
@@ -8190,7 +8223,7 @@
         <v>162721</v>
       </c>
       <c r="G136" s="3">
-        <v>0</v>
+        <v>138353</v>
       </c>
       <c r="H136" s="3">
         <v>10489</v>
@@ -8200,7 +8233,7 @@
       </c>
       <c r="J136" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.5813318106582442E-2</v>
       </c>
       <c r="K136" s="5">
         <v>7.5048539722438759E-2</v>
@@ -8235,7 +8268,7 @@
         <v>146664</v>
       </c>
       <c r="G137" s="3">
-        <v>0</v>
+        <v>149505</v>
       </c>
       <c r="H137" s="3">
         <v>10264</v>
@@ -8245,7 +8278,7 @@
       </c>
       <c r="J137" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.8653222300257513E-2</v>
       </c>
       <c r="K137" s="5">
         <v>7.3519668926281825E-2</v>
@@ -8280,7 +8313,7 @@
         <v>369226</v>
       </c>
       <c r="G138" s="3">
-        <v>0</v>
+        <v>191973</v>
       </c>
       <c r="H138" s="3">
         <v>16212</v>
@@ -8290,7 +8323,7 @@
       </c>
       <c r="J138" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.4449375693456896E-2</v>
       </c>
       <c r="K138" s="5">
         <v>7.8510788530939471E-2</v>
@@ -8325,7 +8358,7 @@
         <v>583256</v>
       </c>
       <c r="G139" s="3">
-        <v>0</v>
+        <v>216044</v>
       </c>
       <c r="H139" s="3">
         <v>21800</v>
@@ -8335,7 +8368,7 @@
       </c>
       <c r="J139" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.10090537112810354</v>
       </c>
       <c r="K139" s="5">
         <v>7.5715589641938363E-2</v>
@@ -8370,7 +8403,7 @@
         <v>432355</v>
       </c>
       <c r="G140" s="3">
-        <v>0</v>
+        <v>231263</v>
       </c>
       <c r="H140" s="3">
         <v>19538</v>
@@ -8380,7 +8413,7 @@
       </c>
       <c r="J140" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.4483899283499739E-2</v>
       </c>
       <c r="K140" s="5">
         <v>8.1943821196490629E-2</v>
@@ -8415,7 +8448,7 @@
         <v>373662</v>
       </c>
       <c r="G141" s="3">
-        <v>0</v>
+        <v>234105</v>
       </c>
       <c r="H141" s="3">
         <v>19804</v>
@@ -8425,7 +8458,7 @@
       </c>
       <c r="J141" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.4594519553191944E-2</v>
       </c>
       <c r="K141" s="5">
         <v>7.63425660863081E-2</v>
@@ -8460,7 +8493,7 @@
         <v>377163</v>
       </c>
       <c r="G142" s="3">
-        <v>0</v>
+        <v>184181</v>
       </c>
       <c r="H142" s="3">
         <v>16071</v>
@@ -8470,7 +8503,7 @@
       </c>
       <c r="J142" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.7256557408201721E-2</v>
       </c>
       <c r="K142" s="5">
         <v>7.4650696635872399E-2</v>
@@ -8505,7 +8538,7 @@
         <v>264291</v>
       </c>
       <c r="G143" s="3">
-        <v>0</v>
+        <v>176112</v>
       </c>
       <c r="H143" s="3">
         <v>14286</v>
@@ -8515,7 +8548,7 @@
       </c>
       <c r="J143" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.1118833469610255E-2</v>
       </c>
       <c r="K143" s="5">
         <v>7.1175700062198144E-2</v>
@@ -8550,7 +8583,7 @@
         <v>439401</v>
       </c>
       <c r="G144" s="3">
-        <v>0</v>
+        <v>217321</v>
       </c>
       <c r="H144" s="3">
         <v>17880</v>
@@ -8560,7 +8593,7 @@
       </c>
       <c r="J144" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.2274607608100458E-2</v>
       </c>
       <c r="K144" s="5">
         <v>8.3626038896161561E-2</v>
@@ -8595,7 +8628,7 @@
         <v>316295</v>
       </c>
       <c r="G145" s="3">
-        <v>0</v>
+        <v>236867</v>
       </c>
       <c r="H145" s="3">
         <v>17955</v>
@@ -8605,7 +8638,7 @@
       </c>
       <c r="J145" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.5802032364153726E-2</v>
       </c>
       <c r="K145" s="5">
         <v>7.3896198726416631E-2</v>
@@ -8640,7 +8673,7 @@
         <v>395062</v>
       </c>
       <c r="G146" s="3">
-        <v>0</v>
+        <v>215088</v>
       </c>
       <c r="H146" s="3">
         <v>18074</v>
@@ -8650,7 +8683,7 @@
       </c>
       <c r="J146" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.4030722309008404E-2</v>
       </c>
       <c r="K146" s="5">
         <v>7.6284317550891698E-2</v>
@@ -8685,7 +8718,7 @@
         <v>343791</v>
       </c>
       <c r="G147" s="3">
-        <v>0</v>
+        <v>192820</v>
       </c>
       <c r="H147" s="3">
         <v>17513</v>
@@ -8695,7 +8728,7 @@
       </c>
       <c r="J147" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.0825640493724713E-2</v>
       </c>
       <c r="K147" s="5">
         <v>7.4733799500326187E-2</v>
@@ -8730,7 +8763,7 @@
         <v>329306</v>
       </c>
       <c r="G148" s="3">
-        <v>0</v>
+        <v>194053</v>
       </c>
       <c r="H148" s="3">
         <v>17955</v>
@@ -8740,7 +8773,7 @@
       </c>
       <c r="J148" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.2526268596723582E-2</v>
       </c>
       <c r="K148" s="5">
         <v>7.5526788876653317E-2</v>
@@ -8775,7 +8808,7 @@
         <v>320109</v>
       </c>
       <c r="G149" s="3">
-        <v>0</v>
+        <v>175830</v>
       </c>
       <c r="H149" s="3">
         <v>14808</v>
@@ -8785,7 +8818,7 @@
       </c>
       <c r="J149" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.4217710288346695E-2</v>
       </c>
       <c r="K149" s="5">
         <v>8.071161879053175E-2</v>
@@ -8820,7 +8853,7 @@
         <v>346418</v>
       </c>
       <c r="G150" s="3">
-        <v>0</v>
+        <v>277698</v>
       </c>
       <c r="H150" s="3">
         <v>20372</v>
@@ -8830,7 +8863,7 @@
       </c>
       <c r="J150" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.3360269069276701E-2</v>
       </c>
       <c r="K150" s="5">
         <v>6.7678037181433615E-2</v>
@@ -8865,7 +8898,7 @@
         <v>314283</v>
       </c>
       <c r="G151" s="3">
-        <v>0</v>
+        <v>203344</v>
       </c>
       <c r="H151" s="3">
         <v>16583</v>
@@ -8875,7 +8908,7 @@
       </c>
       <c r="J151" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.1551459595562203E-2</v>
       </c>
       <c r="K151" s="5">
         <v>7.4644306241649541E-2</v>
@@ -8910,7 +8943,7 @@
         <v>319819</v>
       </c>
       <c r="G152" s="3">
-        <v>0</v>
+        <v>174971</v>
       </c>
       <c r="H152" s="3">
         <v>14281</v>
@@ -8920,7 +8953,7 @@
       </c>
       <c r="J152" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.1619239759731607E-2</v>
       </c>
       <c r="K152" s="5">
         <v>7.6193402352711381E-2</v>
@@ -8955,7 +8988,7 @@
         <v>242304</v>
       </c>
       <c r="G153" s="3">
-        <v>0</v>
+        <v>166492</v>
       </c>
       <c r="H153" s="3">
         <v>13660</v>
@@ -8965,7 +8998,7 @@
       </c>
       <c r="J153" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.2045984191432622E-2</v>
       </c>
       <c r="K153" s="5">
         <v>7.9748213371700988E-2</v>
@@ -9000,7 +9033,7 @@
         <v>249683</v>
       </c>
       <c r="G154" s="3">
-        <v>0</v>
+        <v>185415</v>
       </c>
       <c r="H154" s="3">
         <v>15460</v>
@@ -9010,7 +9043,7 @@
       </c>
       <c r="J154" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.3380524768761968E-2</v>
       </c>
       <c r="K154" s="5">
         <v>7.7903800324540501E-2</v>
@@ -9045,7 +9078,7 @@
         <v>334165</v>
       </c>
       <c r="G155" s="3">
-        <v>0</v>
+        <v>291733</v>
       </c>
       <c r="H155" s="3">
         <v>21262</v>
@@ -9055,7 +9088,7 @@
       </c>
       <c r="J155" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.2881710331021865E-2</v>
       </c>
       <c r="K155" s="5">
         <v>7.2790311647787292E-2</v>
@@ -9090,7 +9123,7 @@
         <v>292069</v>
       </c>
       <c r="G156" s="3">
-        <v>0</v>
+        <v>203238</v>
       </c>
       <c r="H156" s="3">
         <v>16382</v>
@@ -9100,7 +9133,7 @@
       </c>
       <c r="J156" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.0605004969543093E-2</v>
       </c>
       <c r="K156" s="5">
         <v>7.8976358962682042E-2</v>
@@ -9135,7 +9168,7 @@
         <v>262276</v>
       </c>
       <c r="G157" s="3">
-        <v>0</v>
+        <v>141623</v>
       </c>
       <c r="H157" s="3">
         <v>12400</v>
@@ -9145,7 +9178,7 @@
       </c>
       <c r="J157" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.7556399737330801E-2</v>
       </c>
       <c r="K157" s="5">
         <v>7.4227730637918168E-2</v>
@@ -9180,7 +9213,7 @@
         <v>205215</v>
       </c>
       <c r="G158" s="3">
-        <v>0</v>
+        <v>139931</v>
       </c>
       <c r="H158" s="3">
         <v>11700</v>
@@ -9190,7 +9223,7 @@
       </c>
       <c r="J158" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.361263765713102E-2</v>
       </c>
       <c r="K158" s="5">
         <v>7.7007173110116456E-2</v>
@@ -9225,7 +9258,7 @@
         <v>268538</v>
       </c>
       <c r="G159" s="3">
-        <v>0</v>
+        <v>165435</v>
       </c>
       <c r="H159" s="3">
         <v>12635</v>
@@ -9235,7 +9268,7 @@
       </c>
       <c r="J159" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.6374406866745251E-2</v>
       </c>
       <c r="K159" s="5">
         <v>7.5867459390103142E-2</v>
@@ -9270,7 +9303,7 @@
         <v>248126</v>
       </c>
       <c r="G160" s="3">
-        <v>0</v>
+        <v>206192</v>
       </c>
       <c r="H160" s="3">
         <v>16925</v>
@@ -9280,7 +9313,7 @@
       </c>
       <c r="J160" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.2083688988903544E-2</v>
       </c>
       <c r="K160" s="5">
         <v>7.2592631975716609E-2</v>
@@ -9315,7 +9348,7 @@
         <v>250538</v>
       </c>
       <c r="G161" s="3">
-        <v>0</v>
+        <v>182741</v>
       </c>
       <c r="H161" s="3">
         <v>15341</v>
@@ -9325,7 +9358,7 @@
       </c>
       <c r="J161" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.3949414745459416E-2</v>
       </c>
       <c r="K161" s="5">
         <v>6.9393947978974704E-2</v>
@@ -9360,7 +9393,7 @@
         <v>335332</v>
       </c>
       <c r="G162" s="3">
-        <v>0</v>
+        <v>161651</v>
       </c>
       <c r="H162" s="3">
         <v>14125</v>
@@ -9370,7 +9403,7 @@
       </c>
       <c r="J162" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.7379601734601089E-2</v>
       </c>
       <c r="K162" s="5">
         <v>8.9875475879966693E-2</v>
@@ -9405,7 +9438,7 @@
         <v>369638</v>
       </c>
       <c r="G163" s="3">
-        <v>0</v>
+        <v>137002</v>
       </c>
       <c r="H163" s="3">
         <v>12466</v>
@@ -9415,7 +9448,7 @@
       </c>
       <c r="J163" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.0991372388724248E-2</v>
       </c>
       <c r="K163" s="5">
         <v>7.9989572036068601E-2</v>
@@ -9450,7 +9483,7 @@
         <v>357896</v>
       </c>
       <c r="G164" s="3">
-        <v>0</v>
+        <v>124784</v>
       </c>
       <c r="H164" s="3">
         <v>11668</v>
@@ -9460,7 +9493,7 @@
       </c>
       <c r="J164" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.3505577638158741E-2</v>
       </c>
       <c r="K164" s="5">
         <v>7.639087192236127E-2</v>
@@ -9495,7 +9528,7 @@
         <v>330727</v>
       </c>
       <c r="G165" s="3">
-        <v>0</v>
+        <v>184647</v>
       </c>
       <c r="H165" s="3">
         <v>15264</v>
@@ -9505,7 +9538,7 @@
       </c>
       <c r="J165" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.2665843474305029E-2</v>
       </c>
       <c r="K165" s="5">
         <v>7.0900382033696557E-2</v>
@@ -9540,7 +9573,7 @@
         <v>307661</v>
       </c>
       <c r="G166" s="3">
-        <v>0</v>
+        <v>192776</v>
       </c>
       <c r="H166" s="3">
         <v>14781</v>
@@ -9550,7 +9583,7 @@
       </c>
       <c r="J166" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.6674482300701327E-2</v>
       </c>
       <c r="K166" s="5">
         <v>8.7933096337033945E-2</v>
@@ -9585,7 +9618,7 @@
         <v>292179</v>
       </c>
       <c r="G167" s="3">
-        <v>0</v>
+        <v>167208</v>
       </c>
       <c r="H167" s="3">
         <v>13924</v>
@@ -9595,7 +9628,7 @@
       </c>
       <c r="J167" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.3273527582412327E-2</v>
       </c>
       <c r="K167" s="5">
         <v>6.944215908881049E-2</v>
@@ -9630,7 +9663,7 @@
         <v>228639</v>
       </c>
       <c r="G168" s="3">
-        <v>0</v>
+        <v>179515</v>
       </c>
       <c r="H168" s="3">
         <v>13041</v>
@@ -9640,7 +9673,7 @@
       </c>
       <c r="J168" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.2645739910313895E-2</v>
       </c>
       <c r="K168" s="5">
         <v>8.1022479022229116E-2</v>
@@ -9675,7 +9708,7 @@
         <v>249674</v>
       </c>
       <c r="G169" s="3">
-        <v>0</v>
+        <v>241436</v>
       </c>
       <c r="H169" s="3">
         <v>15820</v>
@@ -9685,7 +9718,7 @@
       </c>
       <c r="J169" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.5524611077055622E-2</v>
       </c>
       <c r="K169" s="5">
         <v>7.5927717996247174E-2</v>
@@ -9720,7 +9753,7 @@
         <v>231478</v>
       </c>
       <c r="G170" s="3">
-        <v>0</v>
+        <v>230525</v>
       </c>
       <c r="H170" s="3">
         <v>15807</v>
@@ -9730,7 +9763,7 @@
       </c>
       <c r="J170" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.8569569461012905E-2</v>
       </c>
       <c r="K170" s="5">
         <v>6.9563098086950936E-2</v>
@@ -9765,7 +9798,7 @@
         <v>226323</v>
       </c>
       <c r="G171" s="3">
-        <v>0</v>
+        <v>223423</v>
       </c>
       <c r="H171" s="3">
         <v>16535</v>
@@ -9775,7 +9808,7 @@
       </c>
       <c r="J171" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.4007599933757939E-2</v>
       </c>
       <c r="K171" s="5">
         <v>6.794143861791696E-2</v>
@@ -9810,7 +9843,7 @@
         <v>252151</v>
       </c>
       <c r="G172" s="3">
-        <v>0</v>
+        <v>184875</v>
       </c>
       <c r="H172" s="3">
         <v>14546</v>
@@ -9820,7 +9853,7 @@
       </c>
       <c r="J172" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.8680189317106158E-2</v>
       </c>
       <c r="K172" s="5">
         <v>9.0275690184324867E-2</v>
@@ -9855,7 +9888,7 @@
         <v>218689</v>
       </c>
       <c r="G173" s="3">
-        <v>0</v>
+        <v>192429</v>
       </c>
       <c r="H173" s="3">
         <v>14820</v>
@@ -9865,7 +9898,7 @@
       </c>
       <c r="J173" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.7015418673900507E-2</v>
       </c>
       <c r="K173" s="5">
         <v>7.2072272019244335E-2</v>
@@ -9900,7 +9933,7 @@
         <v>267245</v>
       </c>
       <c r="G174" s="3">
-        <v>0</v>
+        <v>227366</v>
       </c>
       <c r="H174" s="3">
         <v>18246</v>
@@ -9910,7 +9943,7 @@
       </c>
       <c r="J174" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.0249465619309832E-2</v>
       </c>
       <c r="K174" s="5">
         <v>9.2115752646875854E-2</v>
@@ -9945,7 +9978,7 @@
         <v>257887</v>
       </c>
       <c r="G175" s="3">
-        <v>0</v>
+        <v>182420</v>
       </c>
       <c r="H175" s="3">
         <v>17497</v>
@@ -9955,7 +9988,7 @@
       </c>
       <c r="J175" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.5916017980484602E-2</v>
       </c>
       <c r="K175" s="5">
         <v>8.0086471564766754E-2</v>
@@ -9990,7 +10023,7 @@
         <v>267503</v>
       </c>
       <c r="G176" s="3">
-        <v>0</v>
+        <v>182644</v>
       </c>
       <c r="H176" s="3">
         <v>17532</v>
@@ -10000,7 +10033,7 @@
       </c>
       <c r="J176" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.599001335932196E-2</v>
       </c>
       <c r="K176" s="5">
         <v>8.0919988856647057E-2</v>
@@ -10035,7 +10068,7 @@
         <v>204087</v>
       </c>
       <c r="G177" s="3">
-        <v>0</v>
+        <v>153062</v>
       </c>
       <c r="H177" s="3">
         <v>15145</v>
@@ -10045,7 +10078,7 @@
       </c>
       <c r="J177" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.8946832002717852E-2</v>
       </c>
       <c r="K177" s="5">
         <v>6.4471063834369943E-2</v>
@@ -10080,7 +10113,7 @@
         <v>234379</v>
       </c>
       <c r="G178" s="3">
-        <v>0</v>
+        <v>158710</v>
       </c>
       <c r="H178" s="3">
         <v>15673</v>
@@ -10090,7 +10123,7 @@
       </c>
       <c r="J178" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.8752441560078133E-2</v>
       </c>
       <c r="K178" s="5">
         <v>7.4517168579460821E-2</v>
@@ -10125,7 +10158,7 @@
         <v>252172</v>
       </c>
       <c r="G179" s="3">
-        <v>0</v>
+        <v>163251</v>
       </c>
       <c r="H179" s="3">
         <v>15252</v>
@@ -10135,7 +10168,7 @@
       </c>
       <c r="J179" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.3426686513405743E-2</v>
       </c>
       <c r="K179" s="5">
         <v>6.1846073219900648E-2</v>
@@ -10170,7 +10203,7 @@
         <v>306882</v>
       </c>
       <c r="G180" s="3">
-        <v>0</v>
+        <v>181663</v>
       </c>
       <c r="H180" s="3">
         <v>15527</v>
@@ -10180,7 +10213,7 @@
       </c>
       <c r="J180" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.5471449882474695E-2</v>
       </c>
       <c r="K180" s="5">
         <v>7.206000493432993E-2</v>
@@ -10215,7 +10248,7 @@
         <v>219618</v>
       </c>
       <c r="G181" s="3">
-        <v>0</v>
+        <v>156231</v>
       </c>
       <c r="H181" s="3">
         <v>13123</v>
@@ -10225,7 +10258,7 @@
       </c>
       <c r="J181" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.3997414085552807E-2</v>
       </c>
       <c r="K181" s="5">
         <v>9.6572410520125565E-2</v>
@@ -10260,7 +10293,7 @@
         <v>176731</v>
       </c>
       <c r="G182" s="3">
-        <v>0</v>
+        <v>167226</v>
       </c>
       <c r="H182" s="3">
         <v>13784</v>
@@ -10270,7 +10303,7 @@
       </c>
       <c r="J182" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.2427373733749532E-2</v>
       </c>
       <c r="K182" s="5">
         <v>7.1166020155907936E-2</v>
@@ -10305,7 +10338,7 @@
         <v>200170</v>
       </c>
       <c r="G183" s="3">
-        <v>0</v>
+        <v>145990</v>
       </c>
       <c r="H183" s="3">
         <v>13184</v>
@@ -10315,7 +10348,7 @@
       </c>
       <c r="J183" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.0307555312007667E-2</v>
       </c>
       <c r="K183" s="5">
         <v>7.1670593260954263E-2</v>
@@ -10350,7 +10383,7 @@
         <v>155338</v>
       </c>
       <c r="G184" s="3">
-        <v>0</v>
+        <v>159454</v>
       </c>
       <c r="H184" s="3">
         <v>12329</v>
@@ -10360,7 +10393,7 @@
       </c>
       <c r="J184" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.7320104857827338E-2</v>
       </c>
       <c r="K184" s="5">
         <v>7.9164747976225011E-2</v>
@@ -10395,7 +10428,7 @@
         <v>256550</v>
       </c>
       <c r="G185" s="3">
-        <v>0</v>
+        <v>161079</v>
       </c>
       <c r="H185" s="3">
         <v>13731</v>
@@ -10405,7 +10438,7 @@
       </c>
       <c r="J185" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.5243886540144892E-2</v>
       </c>
       <c r="K185" s="5">
         <v>6.6585314357600026E-2</v>
@@ -10440,7 +10473,7 @@
         <v>310741</v>
       </c>
       <c r="G186" s="3">
-        <v>0</v>
+        <v>176757</v>
       </c>
       <c r="H186" s="3">
         <v>14542</v>
@@ -10450,7 +10483,7 @@
       </c>
       <c r="J186" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.2271140605464005E-2</v>
       </c>
       <c r="K186" s="5">
         <v>7.3373583561051212E-2</v>
@@ -10485,7 +10518,7 @@
         <v>261751</v>
       </c>
       <c r="G187" s="3">
-        <v>0</v>
+        <v>179173</v>
       </c>
       <c r="H187" s="3">
         <v>14278</v>
@@ -10495,7 +10528,7 @@
       </c>
       <c r="J187" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.968834590033097E-2</v>
       </c>
       <c r="K187" s="5">
         <v>6.6121436107200907E-2</v>
@@ -10530,7 +10563,7 @@
         <v>329175</v>
       </c>
       <c r="G188" s="3">
-        <v>0</v>
+        <v>178712</v>
       </c>
       <c r="H188" s="3">
         <v>14281</v>
@@ -10540,7 +10573,7 @@
       </c>
       <c r="J188" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.99106943014459E-2</v>
       </c>
       <c r="K188" s="5">
         <v>8.3993017679194773E-2</v>
@@ -10575,7 +10608,7 @@
         <v>299164</v>
       </c>
       <c r="G189" s="3">
-        <v>0</v>
+        <v>174292</v>
       </c>
       <c r="H189" s="3">
         <v>14316</v>
@@ -10585,7 +10618,7 @@
       </c>
       <c r="J189" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.2138021251692561E-2</v>
       </c>
       <c r="K189" s="5">
         <v>8.4704774226105201E-2</v>
@@ -10620,7 +10653,7 @@
         <v>292517</v>
       </c>
       <c r="G190" s="3">
-        <v>0</v>
+        <v>187702</v>
       </c>
       <c r="H190" s="3">
         <v>15912</v>
@@ -10630,7 +10663,7 @@
       </c>
       <c r="J190" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.4772671575156361E-2</v>
       </c>
       <c r="K190" s="5">
         <v>7.899219725298473E-2</v>
@@ -10665,7 +10698,7 @@
         <v>311512</v>
       </c>
       <c r="G191" s="3">
-        <v>0</v>
+        <v>302728</v>
       </c>
       <c r="H191" s="3">
         <v>20257</v>
@@ -10675,7 +10708,7 @@
       </c>
       <c r="J191" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.6914854258608394E-2</v>
       </c>
       <c r="K191" s="5">
         <v>6.7823237331340255E-2</v>
@@ -10710,7 +10743,7 @@
         <v>329701</v>
       </c>
       <c r="G192" s="3">
-        <v>0</v>
+        <v>218175</v>
       </c>
       <c r="H192" s="3">
         <v>18130</v>
@@ -10720,7 +10753,7 @@
       </c>
       <c r="J192" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.3098430159275816E-2</v>
       </c>
       <c r="K192" s="5">
         <v>7.6112344470679688E-2</v>
@@ -10755,7 +10788,7 @@
         <v>327960</v>
       </c>
       <c r="G193" s="3">
-        <v>0</v>
+        <v>197661</v>
       </c>
       <c r="H193" s="3">
         <v>17212</v>
@@ -10765,7 +10798,7 @@
       </c>
       <c r="J193" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.7078381673673613E-2</v>
       </c>
       <c r="K193" s="5">
         <v>7.2819437172067375E-2</v>
@@ -10800,7 +10833,7 @@
         <v>331600</v>
       </c>
       <c r="G194" s="3">
-        <v>0</v>
+        <v>210032</v>
       </c>
       <c r="H194" s="3">
         <v>17995</v>
@@ -10810,7 +10843,7 @@
       </c>
       <c r="J194" s="5">
         <f t="shared" ref="J194:J257" si="3">IFERROR(H194/G194,0)</f>
-        <v>0</v>
+        <v>8.5677420583530131E-2</v>
       </c>
       <c r="K194" s="5">
         <v>6.9191866287157774E-2</v>
@@ -10845,7 +10878,7 @@
         <v>318710</v>
       </c>
       <c r="G195" s="3">
-        <v>0</v>
+        <v>204576</v>
       </c>
       <c r="H195" s="3">
         <v>18051</v>
@@ -10855,7 +10888,7 @@
       </c>
       <c r="J195" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.8236156733927734E-2</v>
       </c>
       <c r="K195" s="5">
         <v>7.4302847625659321E-2</v>
@@ -16569,7 +16602,7 @@
         <v>1100</v>
       </c>
       <c r="J322" s="5">
-        <f t="shared" ref="J322:J381" si="5">IFERROR(H322/G322,0)</f>
+        <f t="shared" ref="J322:J388" si="5">IFERROR(H322/G322,0)</f>
         <v>5.9799653005755113E-2</v>
       </c>
       <c r="K322" s="5">
@@ -18252,10 +18285,10 @@
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C360" s="3">
         <v>208</v>
@@ -18264,10 +18297,10 @@
         <v>270960</v>
       </c>
       <c r="E360" s="3">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F360" s="4">
-        <v>266881</v>
+        <v>268465</v>
       </c>
       <c r="G360" s="3">
         <v>127231</v>
@@ -18289,7 +18322,7 @@
         <v>0.38660124454475248</v>
       </c>
       <c r="M360" s="5">
-        <v>0.99335171568627445</v>
+        <v>0.99647671568627449</v>
       </c>
       <c r="N360" s="3">
         <v>228</v>
@@ -18297,10 +18330,10 @@
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C361" s="3">
         <v>217</v>
@@ -18342,10 +18375,10 @@
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C362" s="3">
         <v>281</v>
@@ -18354,10 +18387,10 @@
         <v>353014</v>
       </c>
       <c r="E362" s="3">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F362" s="4">
-        <v>345646</v>
+        <v>353014</v>
       </c>
       <c r="G362" s="3">
         <v>137295</v>
@@ -18379,7 +18412,7 @@
         <v>0.42495464403416899</v>
       </c>
       <c r="M362" s="5">
-        <v>0.99721511793123041</v>
+        <v>1</v>
       </c>
       <c r="N362" s="3">
         <v>222</v>
@@ -18387,16 +18420,16 @@
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C363" s="3">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D363" s="4">
-        <v>266921</v>
+        <v>266277</v>
       </c>
       <c r="E363" s="3">
         <v>203</v>
@@ -18421,10 +18454,10 @@
         <v>0.13398750295266759</v>
       </c>
       <c r="L363" s="5">
-        <v>0.42705380495423351</v>
+        <v>0.42377511642964338</v>
       </c>
       <c r="M363" s="5">
-        <v>0.98633879781420764</v>
+        <v>0.99180327868852458</v>
       </c>
       <c r="N363" s="3">
         <v>264</v>
@@ -18432,16 +18465,16 @@
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C364" s="3">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D364" s="4">
-        <v>280196</v>
+        <v>272706</v>
       </c>
       <c r="E364" s="3">
         <v>207</v>
@@ -18466,10 +18499,10 @@
         <v>0.10014269601360599</v>
       </c>
       <c r="L364" s="5">
-        <v>0.39255998617303761</v>
+        <v>0.38001627870574289</v>
       </c>
       <c r="M364" s="5">
-        <v>0.99340909090909091</v>
+        <v>0.99669421487603316</v>
       </c>
       <c r="N364" s="3">
         <v>322</v>
@@ -18477,22 +18510,22 @@
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C365" s="3">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D365" s="4">
-        <v>208180</v>
+        <v>206380</v>
       </c>
       <c r="E365" s="3">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F365" s="4">
-        <v>201645</v>
+        <v>203520</v>
       </c>
       <c r="G365" s="3">
         <v>134115</v>
@@ -18511,10 +18544,10 @@
         <v>0.1036548453844163</v>
       </c>
       <c r="L365" s="5">
-        <v>0.36354826632639131</v>
+        <v>0.36895984794677872</v>
       </c>
       <c r="M365" s="5">
-        <v>0.97772435897435894</v>
+        <v>0.99038461538461531</v>
       </c>
       <c r="N365" s="3">
         <v>381</v>
@@ -18522,22 +18555,22 @@
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C366" s="3">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D366" s="4">
-        <v>233178</v>
+        <v>232632</v>
       </c>
       <c r="E366" s="3">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F366" s="4">
-        <v>230311</v>
+        <v>231236</v>
       </c>
       <c r="G366" s="3">
         <v>116574</v>
@@ -18556,10 +18589,10 @@
         <v>0.1034928957614531</v>
       </c>
       <c r="L366" s="5">
-        <v>0.46416523270813009</v>
+        <v>0.45490597344887079</v>
       </c>
       <c r="M366" s="5">
-        <v>0.98099415204678353</v>
+        <v>0.99561403508771928</v>
       </c>
       <c r="N366" s="3">
         <v>296</v>
@@ -18567,22 +18600,22 @@
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C367" s="3">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D367" s="4">
-        <v>279648</v>
+        <v>277748</v>
       </c>
       <c r="E367" s="3">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F367" s="4">
-        <v>274858</v>
+        <v>277748</v>
       </c>
       <c r="G367" s="3">
         <v>117464</v>
@@ -18601,10 +18634,10 @@
         <v>0.10346431228037931</v>
       </c>
       <c r="L367" s="5">
-        <v>0.48406412451543951</v>
+        <v>0.48184190229321727</v>
       </c>
       <c r="M367" s="5">
-        <v>0.98722222222222211</v>
+        <v>1</v>
       </c>
       <c r="N367" s="3">
         <v>293</v>
@@ -18612,22 +18645,22 @@
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C368" s="3">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D368" s="4">
-        <v>219237</v>
+        <v>216537</v>
       </c>
       <c r="E368" s="3">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F368" s="4">
-        <v>207602</v>
+        <v>214997</v>
       </c>
       <c r="G368" s="3">
         <v>138842</v>
@@ -18646,10 +18679,10 @@
         <v>9.9058175737397461E-2</v>
       </c>
       <c r="L368" s="5">
-        <v>0.39066593810934508</v>
+        <v>0.38989886892122327</v>
       </c>
       <c r="M368" s="5">
-        <v>0.95790226722430105</v>
+        <v>0.99152542372881358</v>
       </c>
       <c r="N368" s="3">
         <v>321</v>
@@ -18657,22 +18690,22 @@
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C369" s="3">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D369" s="4">
-        <v>239767</v>
+        <v>235817</v>
       </c>
       <c r="E369" s="3">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F369" s="4">
-        <v>222466</v>
+        <v>233002</v>
       </c>
       <c r="G369" s="3">
         <v>135393</v>
@@ -18691,10 +18724,10 @@
         <v>9.3710131918303408E-2</v>
       </c>
       <c r="L369" s="5">
-        <v>0.4230407315756784</v>
+        <v>0.41042302912746748</v>
       </c>
       <c r="M369" s="5">
-        <v>0.94125683060109278</v>
+        <v>0.98602150537634403</v>
       </c>
       <c r="N369" s="3">
         <v>308</v>
@@ -18702,22 +18735,22 @@
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C370" s="3">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D370" s="4">
-        <v>220724</v>
+        <v>213404</v>
       </c>
       <c r="E370" s="3">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F370" s="4">
-        <v>197689</v>
+        <v>209414</v>
       </c>
       <c r="G370" s="3">
         <v>150030</v>
@@ -18736,10 +18769,10 @@
         <v>9.5145514382973501E-2</v>
       </c>
       <c r="L370" s="5">
-        <v>0.40513028522395339</v>
+        <v>0.39923434346529169</v>
       </c>
       <c r="M370" s="5">
-        <v>0.94413947677836574</v>
+        <v>0.99315476190476193</v>
       </c>
       <c r="N370" s="3">
         <v>291</v>
@@ -18747,22 +18780,22 @@
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C371" s="3">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D371" s="4">
-        <v>266536</v>
+        <v>251826</v>
       </c>
       <c r="E371" s="3">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="F371" s="4">
-        <v>220794</v>
+        <v>245483</v>
       </c>
       <c r="G371" s="3">
         <v>151890</v>
@@ -18781,10 +18814,10 @@
         <v>9.1767601293784459E-2</v>
       </c>
       <c r="L371" s="5">
-        <v>0.42174228098792399</v>
+        <v>0.39336130266386649</v>
       </c>
       <c r="M371" s="5">
-        <v>0.90324422166527429</v>
+        <v>0.98270227631282381</v>
       </c>
       <c r="N371" s="3">
         <v>293</v>
@@ -18792,22 +18825,22 @@
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C372" s="3">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D372" s="4">
-        <v>285550</v>
+        <v>276160</v>
       </c>
       <c r="E372" s="3">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="F372" s="4">
-        <v>245165</v>
+        <v>271720</v>
       </c>
       <c r="G372" s="3">
         <v>198840</v>
@@ -18826,10 +18859,10 @@
         <v>8.9512548342816453E-2</v>
       </c>
       <c r="L372" s="5">
-        <v>0.36606335097681758</v>
+        <v>0.36714532687488882</v>
       </c>
       <c r="M372" s="5">
-        <v>0.90439935564589302</v>
+        <v>0.98518233179250136</v>
       </c>
       <c r="N372" s="3">
         <v>328</v>
@@ -18837,22 +18870,22 @@
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C373" s="3">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D373" s="4">
-        <v>235520</v>
+        <v>233475</v>
       </c>
       <c r="E373" s="3">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="F373" s="4">
-        <v>214885</v>
+        <v>228850</v>
       </c>
       <c r="G373" s="3">
         <v>130475</v>
@@ -18871,10 +18904,10 @@
         <v>9.5580119392953133E-2</v>
       </c>
       <c r="L373" s="5">
-        <v>0.40838397322746811</v>
+        <v>0.40744469429008662</v>
       </c>
       <c r="M373" s="5">
-        <v>0.93763568010936438</v>
+        <v>0.98751515151515168</v>
       </c>
       <c r="N373" s="3">
         <v>278</v>
@@ -18882,22 +18915,22 @@
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C374" s="3">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D374" s="4">
-        <v>224710</v>
+        <v>223360</v>
       </c>
       <c r="E374" s="3">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="F374" s="4">
-        <v>191930</v>
+        <v>209470</v>
       </c>
       <c r="G374" s="3">
         <v>126100</v>
@@ -18916,10 +18949,10 @@
         <v>8.7738638395192747E-2</v>
       </c>
       <c r="L374" s="5">
-        <v>0.37015107540577108</v>
+        <v>0.36943678969148541</v>
       </c>
       <c r="M374" s="5">
-        <v>0.91244202226345095</v>
+        <v>0.96913116123642429</v>
       </c>
       <c r="N374" s="3">
         <v>302</v>
@@ -18927,22 +18960,22 @@
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C375" s="3">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D375" s="4">
-        <v>275960</v>
+        <v>268226</v>
       </c>
       <c r="E375" s="3">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="F375" s="4">
-        <v>207247</v>
+        <v>246051</v>
       </c>
       <c r="G375" s="3">
         <v>122267</v>
@@ -18961,10 +18994,10 @@
         <v>9.5888389992608916E-2</v>
       </c>
       <c r="L375" s="5">
-        <v>0.38578498253581239</v>
+        <v>0.3712795027568816</v>
       </c>
       <c r="M375" s="5">
-        <v>0.82814511769620125</v>
+        <v>0.93567776572994787</v>
       </c>
       <c r="N375" s="3">
         <v>270</v>
@@ -18972,22 +19005,22 @@
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C376" s="3">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D376" s="4">
-        <v>256293</v>
+        <v>251553</v>
       </c>
       <c r="E376" s="3">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="F376" s="4">
-        <v>201362</v>
+        <v>238291</v>
       </c>
       <c r="G376" s="3">
         <v>121131</v>
@@ -19006,10 +19039,10 @@
         <v>8.9883875894926663E-2</v>
       </c>
       <c r="L376" s="5">
-        <v>0.38992681571500393</v>
+        <v>0.39392038471331092</v>
       </c>
       <c r="M376" s="5">
-        <v>0.87356694311711602</v>
+        <v>0.97570919276801649</v>
       </c>
       <c r="N376" s="3">
         <v>253</v>
@@ -19017,22 +19050,22 @@
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C377" s="3">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D377" s="4">
-        <v>241957</v>
+        <v>239582</v>
       </c>
       <c r="E377" s="3">
-        <v>126</v>
+        <v>174</v>
       </c>
       <c r="F377" s="4">
-        <v>167133</v>
+        <v>231237</v>
       </c>
       <c r="G377" s="3">
         <v>116461</v>
@@ -19051,10 +19084,10 @@
         <v>8.2929552174884E-2</v>
       </c>
       <c r="L377" s="5">
-        <v>0.39363960160158429</v>
+        <v>0.3966982218820676</v>
       </c>
       <c r="M377" s="5">
-        <v>0.78208839091192028</v>
+        <v>0.96631089217296118</v>
       </c>
       <c r="N377" s="3">
         <v>299</v>
@@ -19062,22 +19095,22 @@
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C378" s="3">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D378" s="4">
-        <v>285286</v>
+        <v>276906</v>
       </c>
       <c r="E378" s="3">
-        <v>120</v>
+        <v>184</v>
       </c>
       <c r="F378" s="4">
-        <v>158000</v>
+        <v>244336</v>
       </c>
       <c r="G378" s="3">
         <v>124083</v>
@@ -19096,10 +19129,10 @@
         <v>0.1201572105570811</v>
       </c>
       <c r="L378" s="5">
-        <v>0.38588526913703519</v>
+        <v>0.38049695819126289</v>
       </c>
       <c r="M378" s="5">
-        <v>0.69564936087856699</v>
+        <v>0.93108064774731447</v>
       </c>
       <c r="N378" s="3">
         <v>279</v>
@@ -19107,44 +19140,44 @@
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C379" s="3">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D379" s="4">
-        <v>240866</v>
+        <v>229847</v>
       </c>
       <c r="E379" s="3">
-        <v>76</v>
+        <v>157</v>
       </c>
       <c r="F379" s="4">
-        <v>97095</v>
+        <v>194914</v>
       </c>
       <c r="G379" s="3">
         <v>138541</v>
       </c>
       <c r="H379" s="3">
-        <v>11252</v>
+        <v>11253</v>
       </c>
       <c r="I379" s="3">
         <v>951</v>
       </c>
       <c r="J379" s="5">
         <f t="shared" si="5"/>
-        <v>8.1217834431684482E-2</v>
+        <v>8.1225052511530879E-2</v>
       </c>
       <c r="K379" s="5">
-        <v>0.1018402921752028</v>
+        <v>0.1018356749303705</v>
       </c>
       <c r="L379" s="5">
-        <v>0.31489313945774811</v>
+        <v>0.31437734327041328</v>
       </c>
       <c r="M379" s="5">
-        <v>0.59110409110409112</v>
+        <v>0.90584816418149761</v>
       </c>
       <c r="N379" s="3">
         <v>418</v>
@@ -19152,44 +19185,44 @@
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C380" s="3">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D380" s="4">
-        <v>273930</v>
+        <v>260490</v>
       </c>
       <c r="E380" s="3">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="F380" s="4">
-        <v>51646</v>
+        <v>200332</v>
       </c>
       <c r="G380" s="3">
         <v>123681</v>
       </c>
       <c r="H380" s="3">
-        <v>9934</v>
+        <v>9935</v>
       </c>
       <c r="I380" s="3">
         <v>856</v>
       </c>
       <c r="J380" s="5">
         <f t="shared" si="5"/>
-        <v>8.0319531698482383E-2</v>
+        <v>8.0327617014739533E-2</v>
       </c>
       <c r="K380" s="5">
-        <v>0.1099182944211336</v>
+        <v>0.109912770760024</v>
       </c>
       <c r="L380" s="5">
-        <v>0.39758625644594042</v>
+        <v>0.40066648792255449</v>
       </c>
       <c r="M380" s="5">
-        <v>0.48667859917859918</v>
+        <v>0.87225161669606122</v>
       </c>
       <c r="N380" s="3">
         <v>309</v>
@@ -19197,52 +19230,366 @@
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C381" s="3">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D381" s="4">
-        <v>297980</v>
+        <v>283086</v>
       </c>
       <c r="E381" s="3">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="F381" s="4">
-        <v>2745</v>
+        <v>231658</v>
       </c>
       <c r="G381" s="3">
-        <v>118283</v>
+        <v>119369</v>
       </c>
       <c r="H381" s="3">
-        <v>10415</v>
+        <v>10426</v>
       </c>
       <c r="I381" s="3">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="J381" s="5">
         <f t="shared" si="5"/>
-        <v>8.8051537414505887E-2</v>
+        <v>8.7342609890340039E-2</v>
       </c>
       <c r="K381" s="5">
-        <v>8.9429417683614079E-2</v>
+        <v>8.9433709004823905E-2</v>
       </c>
       <c r="L381" s="5">
-        <v>0.3922593040941918</v>
+        <v>0.38137140647899709</v>
       </c>
       <c r="M381" s="5">
-        <v>6.5476190476190479E-2</v>
+        <v>0.87928395401876602</v>
       </c>
       <c r="N381" s="3">
-        <v>290</v>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="382" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A382" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C382" s="3">
+        <v>214</v>
+      </c>
+      <c r="D382" s="4">
+        <v>281489</v>
+      </c>
+      <c r="E382" s="3">
+        <v>158</v>
+      </c>
+      <c r="F382" s="4">
+        <v>206878</v>
+      </c>
+      <c r="G382" s="3">
+        <v>138831</v>
+      </c>
+      <c r="H382" s="3">
+        <v>9388</v>
+      </c>
+      <c r="I382" s="3">
+        <v>862</v>
+      </c>
+      <c r="J382" s="5">
+        <f t="shared" si="5"/>
+        <v>6.7621784759887921E-2</v>
+      </c>
+      <c r="K382" s="5">
+        <v>0.12646542665617719</v>
+      </c>
+      <c r="L382" s="5">
+        <v>0.39732867395923399</v>
+      </c>
+      <c r="M382" s="5">
+        <v>0.87321099602011965</v>
+      </c>
+      <c r="N382" s="3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="383" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A383" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C383" s="3">
+        <v>197</v>
+      </c>
+      <c r="D383" s="4">
+        <v>281400</v>
+      </c>
+      <c r="E383" s="3">
+        <v>148</v>
+      </c>
+      <c r="F383" s="4">
+        <v>203302</v>
+      </c>
+      <c r="G383" s="3">
+        <v>175633</v>
+      </c>
+      <c r="H383" s="3">
+        <v>8873</v>
+      </c>
+      <c r="I383" s="3">
+        <v>767</v>
+      </c>
+      <c r="J383" s="5">
+        <f t="shared" si="5"/>
+        <v>5.0520118656516712E-2</v>
+      </c>
+      <c r="K383" s="5">
+        <v>0.1105625473667334</v>
+      </c>
+      <c r="L383" s="5">
+        <v>0.43624051515164092</v>
+      </c>
+      <c r="M383" s="5">
+        <v>0.84545528167977135</v>
+      </c>
+      <c r="N383" s="3">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="384" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A384" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C384" s="3">
+        <v>188</v>
+      </c>
+      <c r="D384" s="4">
+        <v>261005</v>
+      </c>
+      <c r="E384" s="3">
+        <v>132</v>
+      </c>
+      <c r="F384" s="4">
+        <v>175954</v>
+      </c>
+      <c r="G384" s="3">
+        <v>148592</v>
+      </c>
+      <c r="H384" s="3">
+        <v>9548</v>
+      </c>
+      <c r="I384" s="3">
+        <v>848</v>
+      </c>
+      <c r="J384" s="5">
+        <f t="shared" si="5"/>
+        <v>6.4256487563260467E-2</v>
+      </c>
+      <c r="K384" s="5">
+        <v>0.1101037090177618</v>
+      </c>
+      <c r="L384" s="5">
+        <v>0.37625763470917167</v>
+      </c>
+      <c r="M384" s="5">
+        <v>0.85708845458532568</v>
+      </c>
+      <c r="N384" s="3">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="385" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A385" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B385" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="C385" s="3">
+        <v>175</v>
+      </c>
+      <c r="D385" s="4">
+        <v>231809</v>
+      </c>
+      <c r="E385" s="3">
+        <v>104</v>
+      </c>
+      <c r="F385" s="4">
+        <v>139620</v>
+      </c>
+      <c r="G385" s="3">
+        <v>157368</v>
+      </c>
+      <c r="H385" s="3">
+        <v>10519</v>
+      </c>
+      <c r="I385" s="3">
+        <v>748</v>
+      </c>
+      <c r="J385" s="5">
+        <f t="shared" si="5"/>
+        <v>6.6843322657719487E-2</v>
+      </c>
+      <c r="K385" s="5">
+        <v>8.7245635411950767E-2</v>
+      </c>
+      <c r="L385" s="5">
+        <v>0.42836381704104781</v>
+      </c>
+      <c r="M385" s="5">
+        <v>0.7691382030667745</v>
+      </c>
+      <c r="N385" s="3">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A386" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="C386" s="3">
+        <v>210</v>
+      </c>
+      <c r="D386" s="4">
+        <v>289332</v>
+      </c>
+      <c r="E386" s="3">
+        <v>98</v>
+      </c>
+      <c r="F386" s="4">
+        <v>127854</v>
+      </c>
+      <c r="G386" s="3">
+        <v>164299</v>
+      </c>
+      <c r="H386" s="3">
+        <v>10924</v>
+      </c>
+      <c r="I386" s="3">
+        <v>900</v>
+      </c>
+      <c r="J386" s="5">
+        <f t="shared" si="5"/>
+        <v>6.6488536144468313E-2</v>
+      </c>
+      <c r="K386" s="5">
+        <v>9.7846990519253454E-2</v>
+      </c>
+      <c r="L386" s="5">
+        <v>0.47408505172930582</v>
+      </c>
+      <c r="M386" s="5">
+        <v>0.68993180420727063</v>
+      </c>
+      <c r="N386" s="3">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="387" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A387" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C387" s="3">
+        <v>200</v>
+      </c>
+      <c r="D387" s="4">
+        <v>269046</v>
+      </c>
+      <c r="E387" s="3">
+        <v>34</v>
+      </c>
+      <c r="F387" s="4">
+        <v>40837</v>
+      </c>
+      <c r="G387" s="3">
+        <v>183759</v>
+      </c>
+      <c r="H387" s="3">
+        <v>11885</v>
+      </c>
+      <c r="I387" s="3">
+        <v>1006</v>
+      </c>
+      <c r="J387" s="5">
+        <f t="shared" si="5"/>
+        <v>6.467710425067616E-2</v>
+      </c>
+      <c r="K387" s="5">
+        <v>0.11665644518756919</v>
+      </c>
+      <c r="L387" s="5">
+        <v>0.35460677404251789</v>
+      </c>
+      <c r="M387" s="5">
+        <v>0.48716356107660452</v>
+      </c>
+      <c r="N387" s="3">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="388" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A388" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C388" s="3">
+        <v>236</v>
+      </c>
+      <c r="D388" s="4">
+        <v>313926</v>
+      </c>
+      <c r="E388" s="3">
+        <v>2</v>
+      </c>
+      <c r="F388" s="4">
+        <v>2573</v>
+      </c>
+      <c r="G388" s="3">
+        <v>163273</v>
+      </c>
+      <c r="H388" s="3">
+        <v>10920</v>
+      </c>
+      <c r="I388" s="3">
+        <v>925</v>
+      </c>
+      <c r="J388" s="5">
+        <f t="shared" si="5"/>
+        <v>6.6881848192903909E-2</v>
+      </c>
+      <c r="K388" s="5">
+        <v>0.10346821238271341</v>
+      </c>
+      <c r="L388" s="5">
+        <v>0.38318192947844132</v>
+      </c>
+      <c r="M388" s="5">
+        <v>0.3125</v>
+      </c>
+      <c r="N388" s="3">
+        <v>307</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N381" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="C3:D381">
+  <conditionalFormatting sqref="C3:D388">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>C3&gt;C2</formula>
     </cfRule>
@@ -19250,7 +19597,7 @@
       <formula>C3&lt;C2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G381">
+  <conditionalFormatting sqref="G3:G388">
     <cfRule type="expression" dxfId="3" priority="5">
       <formula>G3&gt;G2</formula>
     </cfRule>
@@ -19258,7 +19605,7 @@
       <formula>G3&lt;G2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:L381">
+  <conditionalFormatting sqref="I3:L388">
     <cfRule type="expression" dxfId="1" priority="7">
       <formula>I3&gt;I2</formula>
     </cfRule>
@@ -19267,5 +19614,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Ежедневная статистика.xlsx
+++ b/Ежедневная статистика.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dergacevad\Folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B767F63C-D915-46F2-A630-92ED050EE5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3121C7F6-4F6C-4819-A7EC-819AA3FE6768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="580">
   <si>
     <t>Обновлено</t>
   </si>
@@ -1588,18 +1588,24 @@
     <t>16.04.2026</t>
   </si>
   <si>
+    <t>26.05.2026 15:56</t>
+  </si>
+  <si>
     <t>17.04.2026</t>
   </si>
   <si>
+    <t>26.05.2026 15:57</t>
+  </si>
+  <si>
+    <t>18.04.2026</t>
+  </si>
+  <si>
+    <t>19.04.2026</t>
+  </si>
+  <si>
     <t>13.05.2026 17:06</t>
   </si>
   <si>
-    <t>18.04.2026</t>
-  </si>
-  <si>
-    <t>19.04.2026</t>
-  </si>
-  <si>
     <t>20.04.2026</t>
   </si>
   <si>
@@ -1609,91 +1615,151 @@
     <t>21.04.2026</t>
   </si>
   <si>
-    <t>13.05.2026 16:53</t>
+    <t>26.05.2026 15:58</t>
   </si>
   <si>
     <t>22.04.2026</t>
   </si>
   <si>
+    <t>26.05.2026 15:59</t>
+  </si>
+  <si>
     <t>23.04.2026</t>
   </si>
   <si>
     <t>24.04.2026</t>
   </si>
   <si>
-    <t>13.05.2026 16:54</t>
-  </si>
-  <si>
     <t>25.04.2026</t>
   </si>
   <si>
+    <t>26.05.2026 16:00</t>
+  </si>
+  <si>
     <t>26.04.2026</t>
   </si>
   <si>
+    <t>18.05.2026 16:14</t>
+  </si>
+  <si>
     <t>27.04.2026</t>
   </si>
   <si>
-    <t>13.05.2026 16:55</t>
+    <t>18.05.2026 16:15</t>
   </si>
   <si>
     <t>28.04.2026</t>
   </si>
   <si>
+    <t>26.05.2026 16:01</t>
+  </si>
+  <si>
     <t>29.04.2026</t>
   </si>
   <si>
     <t>30.04.2026</t>
   </si>
   <si>
-    <t>13.05.2026 16:56</t>
-  </si>
-  <si>
     <t>01.05.2026</t>
   </si>
   <si>
+    <t>26.05.2026 16:02</t>
+  </si>
+  <si>
     <t>02.05.2026</t>
   </si>
   <si>
-    <t>13.05.2026 16:57</t>
-  </si>
-  <si>
     <t>03.05.2026</t>
   </si>
   <si>
+    <t>26.05.2026 16:03</t>
+  </si>
+  <si>
     <t>04.05.2026</t>
   </si>
   <si>
     <t>05.05.2026</t>
   </si>
   <si>
-    <t>13.05.2026 16:58</t>
-  </si>
-  <si>
     <t>06.05.2026</t>
   </si>
   <si>
+    <t>26.05.2026 16:04</t>
+  </si>
+  <si>
     <t>07.05.2026</t>
   </si>
   <si>
     <t>08.05.2026</t>
   </si>
   <si>
-    <t>13.05.2026 16:59</t>
-  </si>
-  <si>
     <t>09.05.2026</t>
   </si>
   <si>
+    <t>26.05.2026 16:05</t>
+  </si>
+  <si>
     <t>10.05.2026</t>
   </si>
   <si>
     <t>11.05.2026</t>
   </si>
   <si>
-    <t>13.05.2026 17:00</t>
-  </si>
-  <si>
     <t>12.05.2026</t>
+  </si>
+  <si>
+    <t>26.05.2026 16:06</t>
+  </si>
+  <si>
+    <t>13.05.2026</t>
+  </si>
+  <si>
+    <t>14.05.2026</t>
+  </si>
+  <si>
+    <t>15.05.2026</t>
+  </si>
+  <si>
+    <t>26.05.2026 16:07</t>
+  </si>
+  <si>
+    <t>16.05.2026</t>
+  </si>
+  <si>
+    <t>17.05.2026</t>
+  </si>
+  <si>
+    <t>26.05.2026 16:08</t>
+  </si>
+  <si>
+    <t>18.05.2026</t>
+  </si>
+  <si>
+    <t>19.05.2026</t>
+  </si>
+  <si>
+    <t>20.05.2026</t>
+  </si>
+  <si>
+    <t>26.05.2026 16:09</t>
+  </si>
+  <si>
+    <t>21.05.2026</t>
+  </si>
+  <si>
+    <t>22.05.2026</t>
+  </si>
+  <si>
+    <t>23.05.2026</t>
+  </si>
+  <si>
+    <t>26.05.2026 16:10</t>
+  </si>
+  <si>
+    <t>24.05.2026</t>
+  </si>
+  <si>
+    <t>25.05.2026</t>
   </si>
 </sst>
 </file>
@@ -2112,7 +2178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N388"/>
+  <dimension ref="A1:N401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -10923,7 +10989,7 @@
         <v>324670</v>
       </c>
       <c r="G196" s="3">
-        <v>0</v>
+        <v>206214</v>
       </c>
       <c r="H196" s="3">
         <v>17122</v>
@@ -10933,7 +10999,7 @@
       </c>
       <c r="J196" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.3030250128507274E-2</v>
       </c>
       <c r="K196" s="5">
         <v>6.9530206291867222E-2</v>
@@ -10968,7 +11034,7 @@
         <v>355476</v>
       </c>
       <c r="G197" s="3">
-        <v>0</v>
+        <v>221404</v>
       </c>
       <c r="H197" s="3">
         <v>18875</v>
@@ -10978,7 +11044,7 @@
       </c>
       <c r="J197" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.5251395638741845E-2</v>
       </c>
       <c r="K197" s="5">
         <v>0.1084240576768522</v>
@@ -11013,7 +11079,7 @@
         <v>338725</v>
       </c>
       <c r="G198" s="3">
-        <v>0</v>
+        <v>223523</v>
       </c>
       <c r="H198" s="3">
         <v>18592</v>
@@ -11023,7 +11089,7 @@
       </c>
       <c r="J198" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.3177122712204107E-2</v>
       </c>
       <c r="K198" s="5">
         <v>7.9057606928038635E-2</v>
@@ -11058,7 +11124,7 @@
         <v>329851</v>
       </c>
       <c r="G199" s="3">
-        <v>0</v>
+        <v>228988</v>
       </c>
       <c r="H199" s="3">
         <v>18650</v>
@@ -11068,7 +11134,7 @@
       </c>
       <c r="J199" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.1445315911750832E-2</v>
       </c>
       <c r="K199" s="5">
         <v>8.0324573914360167E-2</v>
@@ -11103,7 +11169,7 @@
         <v>361288</v>
       </c>
       <c r="G200" s="3">
-        <v>0</v>
+        <v>336865</v>
       </c>
       <c r="H200" s="3">
         <v>17979</v>
@@ -11113,7 +11179,7 @@
       </c>
       <c r="J200" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.3371528653911801E-2</v>
       </c>
       <c r="K200" s="5">
         <v>7.2647075866614036E-2</v>
@@ -11148,7 +11214,7 @@
         <v>413692</v>
       </c>
       <c r="G201" s="3">
-        <v>0</v>
+        <v>243360</v>
       </c>
       <c r="H201" s="3">
         <v>18129</v>
@@ -11158,7 +11224,7 @@
       </c>
       <c r="J201" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.4494575936883634E-2</v>
       </c>
       <c r="K201" s="5">
         <v>7.8130415129009631E-2</v>
@@ -11193,7 +11259,7 @@
         <v>371670</v>
       </c>
       <c r="G202" s="3">
-        <v>0</v>
+        <v>241045</v>
       </c>
       <c r="H202" s="3">
         <v>19670</v>
@@ -11203,7 +11269,7 @@
       </c>
       <c r="J202" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.1603020182953387E-2</v>
       </c>
       <c r="K202" s="5">
         <v>6.0265115149456643E-2</v>
@@ -11238,7 +11304,7 @@
         <v>424555</v>
       </c>
       <c r="G203" s="3">
-        <v>0</v>
+        <v>254944</v>
       </c>
       <c r="H203" s="3">
         <v>19891</v>
@@ -11248,7 +11314,7 @@
       </c>
       <c r="J203" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.802105560436802E-2</v>
       </c>
       <c r="K203" s="5">
         <v>7.2535597953139075E-2</v>
@@ -11283,7 +11349,7 @@
         <v>410013</v>
       </c>
       <c r="G204" s="3">
-        <v>0</v>
+        <v>271983</v>
       </c>
       <c r="H204" s="3">
         <v>21547</v>
@@ -11293,7 +11359,7 @@
       </c>
       <c r="J204" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.9221863131151579E-2</v>
       </c>
       <c r="K204" s="5">
         <v>7.0830650447306506E-2</v>
@@ -11328,7 +11394,7 @@
         <v>428051</v>
       </c>
       <c r="G205" s="3">
-        <v>0</v>
+        <v>285043</v>
       </c>
       <c r="H205" s="3">
         <v>21332</v>
@@ -11338,7 +11404,7 @@
       </c>
       <c r="J205" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.4837831485074183E-2</v>
       </c>
       <c r="K205" s="5">
         <v>7.4635985969536051E-2</v>
@@ -11373,7 +11439,7 @@
         <v>510611</v>
       </c>
       <c r="G206" s="3">
-        <v>0</v>
+        <v>315748</v>
       </c>
       <c r="H206" s="3">
         <v>23122</v>
@@ -11383,7 +11449,7 @@
       </c>
       <c r="J206" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.32292841126468E-2</v>
       </c>
       <c r="K206" s="5">
         <v>8.5202490742502926E-2</v>
@@ -11418,7 +11484,7 @@
         <v>579076</v>
       </c>
       <c r="G207" s="3">
-        <v>0</v>
+        <v>310321</v>
       </c>
       <c r="H207" s="3">
         <v>24434</v>
@@ -11428,7 +11494,7 @@
       </c>
       <c r="J207" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.8737823092861911E-2</v>
       </c>
       <c r="K207" s="5">
         <v>8.9808534169028273E-2</v>
@@ -11463,7 +11529,7 @@
         <v>560810</v>
       </c>
       <c r="G208" s="3">
-        <v>0</v>
+        <v>322061</v>
       </c>
       <c r="H208" s="3">
         <v>25951</v>
@@ -11473,7 +11539,7 @@
       </c>
       <c r="J208" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.0577902943852253E-2</v>
       </c>
       <c r="K208" s="5">
         <v>6.9414134018243909E-2</v>
@@ -11508,7 +11574,7 @@
         <v>516368</v>
       </c>
       <c r="G209" s="3">
-        <v>0</v>
+        <v>313816</v>
       </c>
       <c r="H209" s="3">
         <v>23961</v>
@@ -11518,7 +11584,7 @@
       </c>
       <c r="J209" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.6353659469243121E-2</v>
       </c>
       <c r="K209" s="5">
         <v>7.3410516118465108E-2</v>
@@ -11553,7 +11619,7 @@
         <v>500151</v>
       </c>
       <c r="G210" s="3">
-        <v>0</v>
+        <v>308243</v>
       </c>
       <c r="H210" s="3">
         <v>22099</v>
@@ -11563,7 +11629,7 @@
       </c>
       <c r="J210" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.1693436671716793E-2</v>
       </c>
       <c r="K210" s="5">
         <v>8.1782535264987771E-2</v>
@@ -11598,7 +11664,7 @@
         <v>502100</v>
       </c>
       <c r="G211" s="3">
-        <v>0</v>
+        <v>371928</v>
       </c>
       <c r="H211" s="3">
         <v>24053</v>
@@ -11608,7 +11674,7 @@
       </c>
       <c r="J211" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.4671119141339189E-2</v>
       </c>
       <c r="K211" s="5">
         <v>8.0698787967819693E-2</v>
@@ -11643,7 +11709,7 @@
         <v>473583</v>
       </c>
       <c r="G212" s="3">
-        <v>0</v>
+        <v>372648</v>
       </c>
       <c r="H212" s="3">
         <v>24830</v>
@@ -11653,7 +11719,7 @@
       </c>
       <c r="J212" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.6631244498829997E-2</v>
       </c>
       <c r="K212" s="5">
         <v>7.5759928806090698E-2</v>
@@ -11688,7 +11754,7 @@
         <v>394700</v>
       </c>
       <c r="G213" s="3">
-        <v>0</v>
+        <v>374170</v>
       </c>
       <c r="H213" s="3">
         <v>23820</v>
@@ -11698,7 +11764,7 @@
       </c>
       <c r="J213" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.3660902798193336E-2</v>
       </c>
       <c r="K213" s="5">
         <v>7.7011103975805295E-2</v>
@@ -11733,7 +11799,7 @@
         <v>414283</v>
       </c>
       <c r="G214" s="3">
-        <v>0</v>
+        <v>353295</v>
       </c>
       <c r="H214" s="3">
         <v>22571</v>
@@ -11743,7 +11809,7 @@
       </c>
       <c r="J214" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.3887119829038053E-2</v>
       </c>
       <c r="K214" s="5">
         <v>7.9982174311274773E-2</v>
@@ -11778,7 +11844,7 @@
         <v>482738</v>
       </c>
       <c r="G215" s="3">
-        <v>0</v>
+        <v>376858</v>
       </c>
       <c r="H215" s="3">
         <v>25242</v>
@@ -11788,7 +11854,7 @@
       </c>
       <c r="J215" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.6980135754050596E-2</v>
       </c>
       <c r="K215" s="5">
         <v>7.7328400235126202E-2</v>
@@ -11823,7 +11889,7 @@
         <v>350720</v>
       </c>
       <c r="G216" s="3">
-        <v>0</v>
+        <v>337244</v>
       </c>
       <c r="H216" s="3">
         <v>23422</v>
@@ -11833,7 +11899,7 @@
       </c>
       <c r="J216" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.9451198538743458E-2</v>
       </c>
       <c r="K216" s="5">
         <v>7.0645273735543412E-2</v>
@@ -11868,7 +11934,7 @@
         <v>321838</v>
       </c>
       <c r="G217" s="3">
-        <v>0</v>
+        <v>323167</v>
       </c>
       <c r="H217" s="3">
         <v>22749</v>
@@ -11878,7 +11944,7 @@
       </c>
       <c r="J217" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.0393944926307447E-2</v>
       </c>
       <c r="K217" s="5">
         <v>8.6923936114259567E-2</v>
@@ -11913,7 +11979,7 @@
         <v>390341</v>
       </c>
       <c r="G218" s="3">
-        <v>0</v>
+        <v>353493</v>
       </c>
       <c r="H218" s="3">
         <v>23194</v>
@@ -11923,7 +11989,7 @@
       </c>
       <c r="J218" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.5613746241085402E-2</v>
       </c>
       <c r="K218" s="5">
         <v>8.3723635279242398E-2</v>
@@ -11958,7 +12024,7 @@
         <v>396488</v>
       </c>
       <c r="G219" s="3">
-        <v>0</v>
+        <v>334283</v>
       </c>
       <c r="H219" s="3">
         <v>22239</v>
@@ -11968,7 +12034,7 @@
       </c>
       <c r="J219" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.65274632571803E-2</v>
       </c>
       <c r="K219" s="5">
         <v>7.4960998894071262E-2</v>
@@ -12003,7 +12069,7 @@
         <v>435323</v>
       </c>
       <c r="G220" s="3">
-        <v>0</v>
+        <v>310279</v>
       </c>
       <c r="H220" s="3">
         <v>23201</v>
@@ -12013,7 +12079,7 @@
       </c>
       <c r="J220" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.4774638309392516E-2</v>
       </c>
       <c r="K220" s="5">
         <v>7.5674767943365986E-2</v>
@@ -12048,7 +12114,7 @@
         <v>380414</v>
       </c>
       <c r="G221" s="3">
-        <v>0</v>
+        <v>291608</v>
       </c>
       <c r="H221" s="3">
         <v>22020</v>
@@ -12058,7 +12124,7 @@
       </c>
       <c r="J221" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.5512331623275086E-2</v>
       </c>
       <c r="K221" s="5">
         <v>7.4812682882079914E-2</v>
@@ -12093,7 +12159,7 @@
         <v>388799</v>
       </c>
       <c r="G222" s="3">
-        <v>0</v>
+        <v>299132</v>
       </c>
       <c r="H222" s="3">
         <v>20983</v>
@@ -12103,7 +12169,7 @@
       </c>
       <c r="J222" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.0146289932203842E-2</v>
       </c>
       <c r="K222" s="5">
         <v>7.6100498941523792E-2</v>
@@ -12138,7 +12204,7 @@
         <v>389868</v>
       </c>
       <c r="G223" s="3">
-        <v>0</v>
+        <v>283188</v>
       </c>
       <c r="H223" s="3">
         <v>22528</v>
@@ -12148,7 +12214,7 @@
       </c>
       <c r="J223" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.9551393420625172E-2</v>
       </c>
       <c r="K223" s="5">
         <v>7.8479621543823444E-2</v>
@@ -12183,7 +12249,7 @@
         <v>423441</v>
       </c>
       <c r="G224" s="3">
-        <v>0</v>
+        <v>296142</v>
       </c>
       <c r="H224" s="3">
         <v>24401</v>
@@ -12193,7 +12259,7 @@
       </c>
       <c r="J224" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.239628286430159E-2</v>
       </c>
       <c r="K224" s="5">
         <v>7.008254045030983E-2</v>
@@ -12228,7 +12294,7 @@
         <v>462730</v>
       </c>
       <c r="G225" s="3">
-        <v>0</v>
+        <v>310796</v>
       </c>
       <c r="H225" s="3">
         <v>23719</v>
@@ -12238,7 +12304,7 @@
       </c>
       <c r="J225" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.631694101597189E-2</v>
       </c>
       <c r="K225" s="5">
         <v>8.1774556577669466E-2</v>
@@ -12273,7 +12339,7 @@
         <v>316032</v>
       </c>
       <c r="G226" s="3">
-        <v>0</v>
+        <v>329502</v>
       </c>
       <c r="H226" s="3">
         <v>22628</v>
@@ -12283,7 +12349,7 @@
       </c>
       <c r="J226" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.8673331269612933E-2</v>
       </c>
       <c r="K226" s="5">
         <v>7.9899943564812725E-2</v>
@@ -12318,7 +12384,7 @@
         <v>380145</v>
       </c>
       <c r="G227" s="3">
-        <v>0</v>
+        <v>334884</v>
       </c>
       <c r="H227" s="3">
         <v>25021</v>
@@ -12328,7 +12394,7 @@
       </c>
       <c r="J227" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.4715423848257898E-2</v>
       </c>
       <c r="K227" s="5">
         <v>7.3218948006358628E-2</v>
@@ -12363,7 +12429,7 @@
         <v>411397</v>
       </c>
       <c r="G228" s="3">
-        <v>0</v>
+        <v>309833</v>
       </c>
       <c r="H228" s="3">
         <v>24430</v>
@@ -12373,7 +12439,7 @@
       </c>
       <c r="J228" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.8848928293629147E-2</v>
       </c>
       <c r="K228" s="5">
         <v>8.1443771879314023E-2</v>
@@ -12408,7 +12474,7 @@
         <v>395049</v>
       </c>
       <c r="G229" s="3">
-        <v>0</v>
+        <v>299718</v>
       </c>
       <c r="H229" s="3">
         <v>23108</v>
@@ -12418,7 +12484,7 @@
       </c>
       <c r="J229" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.7099139858133311E-2</v>
       </c>
       <c r="K229" s="5">
         <v>7.0794294651553291E-2</v>
@@ -12453,7 +12519,7 @@
         <v>384258</v>
       </c>
       <c r="G230" s="3">
-        <v>0</v>
+        <v>260471</v>
       </c>
       <c r="H230" s="3">
         <v>20453</v>
@@ -12463,7 +12529,7 @@
       </c>
       <c r="J230" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.8523136932710361E-2</v>
       </c>
       <c r="K230" s="5">
         <v>8.1076891132012496E-2</v>
@@ -12498,7 +12564,7 @@
         <v>430211</v>
       </c>
       <c r="G231" s="3">
-        <v>0</v>
+        <v>244421</v>
       </c>
       <c r="H231" s="3">
         <v>20780</v>
@@ -12508,7 +12574,7 @@
       </c>
       <c r="J231" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.5017244835754707E-2</v>
       </c>
       <c r="K231" s="5">
         <v>8.0513000451438638E-2</v>
@@ -12543,7 +12609,7 @@
         <v>509009</v>
       </c>
       <c r="G232" s="3">
-        <v>0</v>
+        <v>385742</v>
       </c>
       <c r="H232" s="3">
         <v>31744</v>
@@ -12553,7 +12619,7 @@
       </c>
       <c r="J232" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.2293346329930364E-2</v>
       </c>
       <c r="K232" s="5">
         <v>8.0229394578256702E-2</v>
@@ -12588,7 +12654,7 @@
         <v>386085</v>
       </c>
       <c r="G233" s="3">
-        <v>0</v>
+        <v>340793</v>
       </c>
       <c r="H233" s="3">
         <v>25375</v>
@@ -12598,7 +12664,7 @@
       </c>
       <c r="J233" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.4458688998893754E-2</v>
       </c>
       <c r="K233" s="5">
         <v>7.9875307583867808E-2</v>
@@ -12633,7 +12699,7 @@
         <v>367288</v>
       </c>
       <c r="G234" s="3">
-        <v>0</v>
+        <v>277320</v>
       </c>
       <c r="H234" s="3">
         <v>20050</v>
@@ -12643,7 +12709,7 @@
       </c>
       <c r="J234" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.2299148997547955E-2</v>
       </c>
       <c r="K234" s="5">
         <v>0.10371237156059079</v>
@@ -12678,7 +12744,7 @@
         <v>414068</v>
       </c>
       <c r="G235" s="3">
-        <v>0</v>
+        <v>278891</v>
       </c>
       <c r="H235" s="3">
         <v>21417</v>
@@ -12688,7 +12754,7 @@
       </c>
       <c r="J235" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.6793442599438488E-2</v>
       </c>
       <c r="K235" s="5">
         <v>0.12694534381565881</v>
@@ -12723,7 +12789,7 @@
         <v>556518</v>
       </c>
       <c r="G236" s="3">
-        <v>0</v>
+        <v>250015</v>
       </c>
       <c r="H236" s="3">
         <v>20919</v>
@@ -12733,7 +12799,7 @@
       </c>
       <c r="J236" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.3670979741215526E-2</v>
       </c>
       <c r="K236" s="5">
         <v>8.184440027553691E-2</v>
@@ -12768,7 +12834,7 @@
         <v>503883</v>
       </c>
       <c r="G237" s="3">
-        <v>0</v>
+        <v>273835</v>
       </c>
       <c r="H237" s="3">
         <v>23638</v>
@@ -12778,7 +12844,7 @@
       </c>
       <c r="J237" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8.6322055252250438E-2</v>
       </c>
       <c r="K237" s="5">
         <v>7.1198180380648776E-2</v>
@@ -12813,7 +12879,7 @@
         <v>510551</v>
       </c>
       <c r="G238" s="3">
-        <v>0</v>
+        <v>337592</v>
       </c>
       <c r="H238" s="3">
         <v>25097</v>
@@ -12823,7 +12889,7 @@
       </c>
       <c r="J238" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.4341216616507499E-2</v>
       </c>
       <c r="K238" s="5">
         <v>7.4679374616744329E-2</v>
@@ -12858,7 +12924,7 @@
         <v>556095</v>
       </c>
       <c r="G239" s="3">
-        <v>0</v>
+        <v>411186</v>
       </c>
       <c r="H239" s="3">
         <v>29347</v>
@@ -12868,7 +12934,7 @@
       </c>
       <c r="J239" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.1371593390825563E-2</v>
       </c>
       <c r="K239" s="5">
         <v>8.3425559735982049E-2</v>
@@ -12903,7 +12969,7 @@
         <v>591344</v>
       </c>
       <c r="G240" s="3">
-        <v>0</v>
+        <v>430249</v>
       </c>
       <c r="H240" s="3">
         <v>27637</v>
@@ -12913,7 +12979,7 @@
       </c>
       <c r="J240" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.4234896536656677E-2</v>
       </c>
       <c r="K240" s="5">
         <v>8.0097058528113635E-2</v>
@@ -12948,7 +13014,7 @@
         <v>578706</v>
       </c>
       <c r="G241" s="3">
-        <v>0</v>
+        <v>437199</v>
       </c>
       <c r="H241" s="3">
         <v>28298</v>
@@ -12958,7 +13024,7 @@
       </c>
       <c r="J241" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.4725674120938062E-2</v>
       </c>
       <c r="K241" s="5">
         <v>8.0852670040093166E-2</v>
@@ -12993,7 +13059,7 @@
         <v>656046</v>
       </c>
       <c r="G242" s="3">
-        <v>0</v>
+        <v>389173</v>
       </c>
       <c r="H242" s="3">
         <v>29895</v>
@@ -13003,7 +13069,7 @@
       </c>
       <c r="J242" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.6816737029547277E-2</v>
       </c>
       <c r="K242" s="5">
         <v>8.1796789109387369E-2</v>
@@ -13038,7 +13104,7 @@
         <v>646046</v>
       </c>
       <c r="G243" s="3">
-        <v>0</v>
+        <v>412934</v>
       </c>
       <c r="H243" s="3">
         <v>28715</v>
@@ -13048,7 +13114,7 @@
       </c>
       <c r="J243" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.9538957799551507E-2</v>
       </c>
       <c r="K243" s="5">
         <v>8.2908698214347987E-2</v>
@@ -13083,7 +13149,7 @@
         <v>553886</v>
       </c>
       <c r="G244" s="3">
-        <v>0</v>
+        <v>378191</v>
       </c>
       <c r="H244" s="3">
         <v>28690</v>
@@ -13093,7 +13159,7 @@
       </c>
       <c r="J244" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.586113894830919E-2</v>
       </c>
       <c r="K244" s="5">
         <v>7.9839800605854369E-2</v>
@@ -13128,7 +13194,7 @@
         <v>639097</v>
       </c>
       <c r="G245" s="3">
-        <v>0</v>
+        <v>389257</v>
       </c>
       <c r="H245" s="3">
         <v>30378</v>
@@ -13138,7 +13204,7 @@
       </c>
       <c r="J245" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.8040985775464533E-2</v>
       </c>
       <c r="K245" s="5">
         <v>8.19764577586167E-2</v>
@@ -13173,7 +13239,7 @@
         <v>737263</v>
       </c>
       <c r="G246" s="3">
-        <v>0</v>
+        <v>468762</v>
       </c>
       <c r="H246" s="3">
         <v>34661</v>
@@ -13183,7 +13249,7 @@
       </c>
       <c r="J246" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.3941573762378351E-2</v>
       </c>
       <c r="K246" s="5">
         <v>7.982952952452288E-2</v>
@@ -13218,7 +13284,7 @@
         <v>685181</v>
       </c>
       <c r="G247" s="3">
-        <v>0</v>
+        <v>429755</v>
       </c>
       <c r="H247" s="3">
         <v>30039</v>
@@ -13228,7 +13294,7 @@
       </c>
       <c r="J247" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.9897965119661204E-2</v>
       </c>
       <c r="K247" s="5">
         <v>8.4925201001304296E-2</v>
@@ -13263,7 +13329,7 @@
         <v>686160</v>
       </c>
       <c r="G248" s="3">
-        <v>0</v>
+        <v>332168</v>
       </c>
       <c r="H248" s="3">
         <v>25074</v>
@@ -13273,7 +13339,7 @@
       </c>
       <c r="J248" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.5485898701861703E-2</v>
       </c>
       <c r="K248" s="5">
         <v>9.0381464320323332E-2</v>
@@ -13308,7 +13374,7 @@
         <v>674195</v>
       </c>
       <c r="G249" s="3">
-        <v>0</v>
+        <v>297780</v>
       </c>
       <c r="H249" s="3">
         <v>21836</v>
@@ -13318,7 +13384,7 @@
       </c>
       <c r="J249" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.3329303512660357E-2</v>
       </c>
       <c r="K249" s="5">
         <v>8.1108880426834049E-2</v>
@@ -13353,7 +13419,7 @@
         <v>704063</v>
       </c>
       <c r="G250" s="3">
-        <v>0</v>
+        <v>310454</v>
       </c>
       <c r="H250" s="3">
         <v>23356</v>
@@ -13363,7 +13429,7 @@
       </c>
       <c r="J250" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.523175736179917E-2</v>
       </c>
       <c r="K250" s="5">
         <v>7.8502320954873236E-2</v>
@@ -13398,7 +13464,7 @@
         <v>739800</v>
       </c>
       <c r="G251" s="3">
-        <v>0</v>
+        <v>327048</v>
       </c>
       <c r="H251" s="3">
         <v>23158</v>
@@ -13408,7 +13474,7 @@
       </c>
       <c r="J251" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.0809177857684494E-2</v>
       </c>
       <c r="K251" s="5">
         <v>7.5986419150341392E-2</v>
@@ -13443,7 +13509,7 @@
         <v>730396</v>
       </c>
       <c r="G252" s="3">
-        <v>0</v>
+        <v>338219</v>
       </c>
       <c r="H252" s="3">
         <v>24802</v>
@@ -13453,7 +13519,7 @@
       </c>
       <c r="J252" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.3331184824034126E-2</v>
       </c>
       <c r="K252" s="5">
         <v>9.3443029985033343E-2</v>
@@ -13488,7 +13554,7 @@
         <v>592828</v>
       </c>
       <c r="G253" s="3">
-        <v>0</v>
+        <v>292884</v>
       </c>
       <c r="H253" s="3">
         <v>23194</v>
@@ -13498,7 +13564,7 @@
       </c>
       <c r="J253" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.9191761926223347E-2</v>
       </c>
       <c r="K253" s="5">
         <v>7.4214391165716709E-2</v>
@@ -13533,7 +13599,7 @@
         <v>534720</v>
       </c>
       <c r="G254" s="3">
-        <v>0</v>
+        <v>280711</v>
       </c>
       <c r="H254" s="3">
         <v>21340</v>
@@ -13543,7 +13609,7 @@
       </c>
       <c r="J254" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.6021246050208227E-2</v>
       </c>
       <c r="K254" s="5">
         <v>8.8186914404326869E-2</v>
@@ -13578,7 +13644,7 @@
         <v>366547</v>
       </c>
       <c r="G255" s="3">
-        <v>0</v>
+        <v>251091</v>
       </c>
       <c r="H255" s="3">
         <v>16241</v>
@@ -13588,7 +13654,7 @@
       </c>
       <c r="J255" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.4681728934927976E-2</v>
       </c>
       <c r="K255" s="5">
         <v>8.0443740475865791E-2</v>
@@ -13623,7 +13689,7 @@
         <v>238973</v>
       </c>
       <c r="G256" s="3">
-        <v>0</v>
+        <v>153082</v>
       </c>
       <c r="H256" s="3">
         <v>10456</v>
@@ -13633,7 +13699,7 @@
       </c>
       <c r="J256" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.8303262303863285E-2</v>
       </c>
       <c r="K256" s="5">
         <v>8.897599225759345E-2</v>
@@ -13668,7 +13734,7 @@
         <v>286684</v>
       </c>
       <c r="G257" s="3">
-        <v>0</v>
+        <v>127171</v>
       </c>
       <c r="H257" s="3">
         <v>11651</v>
@@ -13678,7 +13744,7 @@
       </c>
       <c r="J257" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9.1616799427542445E-2</v>
       </c>
       <c r="K257" s="5">
         <v>8.9878821560090291E-2</v>
@@ -13713,7 +13779,7 @@
         <v>328029</v>
       </c>
       <c r="G258" s="3">
-        <v>0</v>
+        <v>164755</v>
       </c>
       <c r="H258" s="3">
         <v>14133</v>
@@ -13723,7 +13789,7 @@
       </c>
       <c r="J258" s="5">
         <f t="shared" ref="J258:J321" si="4">IFERROR(H258/G258,0)</f>
-        <v>0</v>
+        <v>8.5781918606415583E-2</v>
       </c>
       <c r="K258" s="5">
         <v>7.462920593638192E-2</v>
@@ -13758,7 +13824,7 @@
         <v>320750</v>
       </c>
       <c r="G259" s="3">
-        <v>0</v>
+        <v>157570</v>
       </c>
       <c r="H259" s="3">
         <v>14836</v>
@@ -13768,7 +13834,7 @@
       </c>
       <c r="J259" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9.4154978739607792E-2</v>
       </c>
       <c r="K259" s="5">
         <v>8.1789412080420232E-2</v>
@@ -13803,7 +13869,7 @@
         <v>262416</v>
       </c>
       <c r="G260" s="3">
-        <v>0</v>
+        <v>145312</v>
       </c>
       <c r="H260" s="3">
         <v>13914</v>
@@ -13813,7 +13879,7 @@
       </c>
       <c r="J260" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9.5752587535785069E-2</v>
       </c>
       <c r="K260" s="5">
         <v>8.1080434097611509E-2</v>
@@ -13848,7 +13914,7 @@
         <v>288621</v>
       </c>
       <c r="G261" s="3">
-        <v>0</v>
+        <v>239647</v>
       </c>
       <c r="H261" s="3">
         <v>16244</v>
@@ -13858,7 +13924,7 @@
       </c>
       <c r="J261" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.7783030874578029E-2</v>
       </c>
       <c r="K261" s="5">
         <v>7.5535648061754543E-2</v>
@@ -13893,7 +13959,7 @@
         <v>249967</v>
       </c>
       <c r="G262" s="3">
-        <v>0</v>
+        <v>265146</v>
       </c>
       <c r="H262" s="3">
         <v>17746</v>
@@ -13903,7 +13969,7 @@
       </c>
       <c r="J262" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.6929163555173379E-2</v>
       </c>
       <c r="K262" s="5">
         <v>9.3856422147481439E-2</v>
@@ -13938,7 +14004,7 @@
         <v>273063</v>
       </c>
       <c r="G263" s="3">
-        <v>0</v>
+        <v>258233</v>
       </c>
       <c r="H263" s="3">
         <v>18122</v>
@@ -13948,7 +14014,7 @@
       </c>
       <c r="J263" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.0176933234714384E-2</v>
       </c>
       <c r="K263" s="5">
         <v>7.5148015952270941E-2</v>
@@ -13983,7 +14049,7 @@
         <v>260968</v>
       </c>
       <c r="G264" s="3">
-        <v>0</v>
+        <v>275606</v>
       </c>
       <c r="H264" s="3">
         <v>18034</v>
@@ -13993,7 +14059,7 @@
       </c>
       <c r="J264" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.5433989100382436E-2</v>
       </c>
       <c r="K264" s="5">
         <v>7.0807578884724318E-2</v>
@@ -14028,7 +14094,7 @@
         <v>267402</v>
       </c>
       <c r="G265" s="3">
-        <v>0</v>
+        <v>291518</v>
       </c>
       <c r="H265" s="3">
         <v>18898</v>
@@ -14038,7 +14104,7 @@
       </c>
       <c r="J265" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.4826185690077462E-2</v>
       </c>
       <c r="K265" s="5">
         <v>8.2727310487460931E-2</v>
@@ -14073,7 +14139,7 @@
         <v>319179</v>
       </c>
       <c r="G266" s="3">
-        <v>0</v>
+        <v>254007</v>
       </c>
       <c r="H266" s="3">
         <v>19127</v>
@@ -14083,7 +14149,7 @@
       </c>
       <c r="J266" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.5301074379839919E-2</v>
       </c>
       <c r="K266" s="5">
         <v>7.5889092957028503E-2</v>
@@ -14118,7 +14184,7 @@
         <v>340616</v>
       </c>
       <c r="G267" s="3">
-        <v>0</v>
+        <v>342337</v>
       </c>
       <c r="H267" s="3">
         <v>21227</v>
@@ -14128,7 +14194,7 @@
       </c>
       <c r="J267" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.2006151832843075E-2</v>
       </c>
       <c r="K267" s="5">
         <v>9.4396888058605979E-2</v>
@@ -14163,7 +14229,7 @@
         <v>282959</v>
       </c>
       <c r="G268" s="3">
-        <v>0</v>
+        <v>271386</v>
       </c>
       <c r="H268" s="3">
         <v>17879</v>
@@ -14173,7 +14239,7 @@
       </c>
       <c r="J268" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.5880332810093367E-2</v>
       </c>
       <c r="K268" s="5">
         <v>9.0398197223687582E-2</v>
@@ -14208,7 +14274,7 @@
         <v>249841</v>
       </c>
       <c r="G269" s="3">
-        <v>0</v>
+        <v>247758</v>
       </c>
       <c r="H269" s="3">
         <v>16268</v>
@@ -14218,7 +14284,7 @@
       </c>
       <c r="J269" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.5660846471153306E-2</v>
       </c>
       <c r="K269" s="5">
         <v>8.3889401535552299E-2</v>
@@ -14253,7 +14319,7 @@
         <v>266216</v>
       </c>
       <c r="G270" s="3">
-        <v>0</v>
+        <v>242346</v>
       </c>
       <c r="H270" s="3">
         <v>15581</v>
@@ -14263,7 +14329,7 @@
       </c>
       <c r="J270" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.4292375364148779E-2</v>
       </c>
       <c r="K270" s="5">
         <v>7.1713681389551892E-2</v>
@@ -14298,7 +14364,7 @@
         <v>312397</v>
       </c>
       <c r="G271" s="3">
-        <v>0</v>
+        <v>271005</v>
       </c>
       <c r="H271" s="3">
         <v>16874</v>
@@ -14308,7 +14374,7 @@
       </c>
       <c r="J271" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.2264533864688845E-2</v>
       </c>
       <c r="K271" s="5">
         <v>7.04640690079084E-2</v>
@@ -14343,7 +14409,7 @@
         <v>263995</v>
       </c>
       <c r="G272" s="3">
-        <v>0</v>
+        <v>319759</v>
       </c>
       <c r="H272" s="3">
         <v>18019</v>
@@ -14353,7 +14419,7 @@
       </c>
       <c r="J272" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5.6351814960642232E-2</v>
       </c>
       <c r="K272" s="5">
         <v>9.4241416422380375E-2</v>
@@ -14388,7 +14454,7 @@
         <v>268215</v>
       </c>
       <c r="G273" s="3">
-        <v>0</v>
+        <v>281886</v>
       </c>
       <c r="H273" s="3">
         <v>17662</v>
@@ -14398,7 +14464,7 @@
       </c>
       <c r="J273" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.2656534911276193E-2</v>
       </c>
       <c r="K273" s="5">
         <v>8.7597991168529607E-2</v>
@@ -14433,7 +14499,7 @@
         <v>242332</v>
       </c>
       <c r="G274" s="3">
-        <v>0</v>
+        <v>299810</v>
       </c>
       <c r="H274" s="3">
         <v>17860</v>
@@ -14443,7 +14509,7 @@
       </c>
       <c r="J274" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5.9571061672392518E-2</v>
       </c>
       <c r="K274" s="5">
         <v>8.7157038058190112E-2</v>
@@ -14478,7 +14544,7 @@
         <v>244110</v>
       </c>
       <c r="G275" s="3">
-        <v>0</v>
+        <v>217726</v>
       </c>
       <c r="H275" s="3">
         <v>15179</v>
@@ -14488,7 +14554,7 @@
       </c>
       <c r="J275" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.9716065146101069E-2</v>
       </c>
       <c r="K275" s="5">
         <v>8.6036153686615449E-2</v>
@@ -14523,7 +14589,7 @@
         <v>261688</v>
       </c>
       <c r="G276" s="3">
-        <v>0</v>
+        <v>195936</v>
       </c>
       <c r="H276" s="3">
         <v>14780</v>
@@ -14533,7 +14599,7 @@
       </c>
       <c r="J276" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.5432794381838975E-2</v>
       </c>
       <c r="K276" s="5">
         <v>8.7063734099342441E-2</v>
@@ -14568,7 +14634,7 @@
         <v>264678</v>
       </c>
       <c r="G277" s="3">
-        <v>0</v>
+        <v>184194</v>
       </c>
       <c r="H277" s="3">
         <v>12498</v>
@@ -14578,7 +14644,7 @@
       </c>
       <c r="J277" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.7852373041467143E-2</v>
       </c>
       <c r="K277" s="5">
         <v>7.6589333888023206E-2</v>
@@ -14613,7 +14679,7 @@
         <v>285622</v>
       </c>
       <c r="G278" s="3">
-        <v>0</v>
+        <v>208409</v>
       </c>
       <c r="H278" s="3">
         <v>15185</v>
@@ -14623,7 +14689,7 @@
       </c>
       <c r="J278" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.2861536689874232E-2</v>
       </c>
       <c r="K278" s="5">
         <v>8.3581393592829678E-2</v>
@@ -14658,7 +14724,7 @@
         <v>306238</v>
       </c>
       <c r="G279" s="3">
-        <v>0</v>
+        <v>180116</v>
       </c>
       <c r="H279" s="3">
         <v>13973</v>
@@ -14668,7 +14734,7 @@
       </c>
       <c r="J279" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.7577783206378106E-2</v>
       </c>
       <c r="K279" s="5">
         <v>9.2105150853793505E-2</v>
@@ -14703,7 +14769,7 @@
         <v>310149</v>
       </c>
       <c r="G280" s="3">
-        <v>0</v>
+        <v>180594</v>
       </c>
       <c r="H280" s="3">
         <v>15048</v>
@@ -14713,7 +14779,7 @@
       </c>
       <c r="J280" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.3325027409548488E-2</v>
       </c>
       <c r="K280" s="5">
         <v>8.8499790576759385E-2</v>
@@ -14748,7 +14814,7 @@
         <v>283288</v>
       </c>
       <c r="G281" s="3">
-        <v>0</v>
+        <v>185048</v>
       </c>
       <c r="H281" s="3">
         <v>14740</v>
@@ -14758,7 +14824,7 @@
       </c>
       <c r="J281" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.9655008430245131E-2</v>
       </c>
       <c r="K281" s="5">
         <v>8.7815901037002264E-2</v>
@@ -14793,7 +14859,7 @@
         <v>284983</v>
       </c>
       <c r="G282" s="3">
-        <v>0</v>
+        <v>188524</v>
       </c>
       <c r="H282" s="3">
         <v>13724</v>
@@ -14803,7 +14869,7 @@
       </c>
       <c r="J282" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.2797097451783324E-2</v>
       </c>
       <c r="K282" s="5">
         <v>8.109326228578094E-2</v>
@@ -14838,7 +14904,7 @@
         <v>269994</v>
       </c>
       <c r="G283" s="3">
-        <v>0</v>
+        <v>177491</v>
       </c>
       <c r="H283" s="3">
         <v>14485</v>
@@ -14848,7 +14914,7 @@
       </c>
       <c r="J283" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.1609771763075309E-2</v>
       </c>
       <c r="K283" s="5">
         <v>8.0748748584487384E-2</v>
@@ -14883,7 +14949,7 @@
         <v>278517</v>
       </c>
       <c r="G284" s="3">
-        <v>0</v>
+        <v>184037</v>
       </c>
       <c r="H284" s="3">
         <v>13653</v>
@@ -14893,7 +14959,7 @@
       </c>
       <c r="J284" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.4186169085564316E-2</v>
       </c>
       <c r="K284" s="5">
         <v>7.997087058725684E-2</v>
@@ -14928,7 +14994,7 @@
         <v>241280</v>
       </c>
       <c r="G285" s="3">
-        <v>0</v>
+        <v>168073</v>
       </c>
       <c r="H285" s="3">
         <v>13348</v>
@@ -14938,7 +15004,7 @@
       </c>
       <c r="J285" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.9417871996096928E-2</v>
       </c>
       <c r="K285" s="5">
         <v>7.0426083604126263E-2</v>
@@ -14973,7 +15039,7 @@
         <v>275136</v>
       </c>
       <c r="G286" s="3">
-        <v>0</v>
+        <v>192236</v>
       </c>
       <c r="H286" s="3">
         <v>13850</v>
@@ -14983,7 +15049,7 @@
       </c>
       <c r="J286" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.2046859069060942E-2</v>
       </c>
       <c r="K286" s="5">
         <v>0.10529275182994099</v>
@@ -15018,7 +15084,7 @@
         <v>285629</v>
       </c>
       <c r="G287" s="3">
-        <v>0</v>
+        <v>222221</v>
       </c>
       <c r="H287" s="3">
         <v>15995</v>
@@ -15028,7 +15094,7 @@
       </c>
       <c r="J287" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.1977895878427331E-2</v>
       </c>
       <c r="K287" s="5">
         <v>7.3418366980006228E-2</v>
@@ -15063,7 +15129,7 @@
         <v>333892</v>
       </c>
       <c r="G288" s="3">
-        <v>0</v>
+        <v>206779</v>
       </c>
       <c r="H288" s="3">
         <v>15870</v>
@@ -15073,7 +15139,7 @@
       </c>
       <c r="J288" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.674860599964213E-2</v>
       </c>
       <c r="K288" s="5">
         <v>9.6502394081709977E-2</v>
@@ -15108,7 +15174,7 @@
         <v>272656</v>
       </c>
       <c r="G289" s="3">
-        <v>0</v>
+        <v>206982</v>
       </c>
       <c r="H289" s="3">
         <v>15037</v>
@@ -15118,7 +15184,7 @@
       </c>
       <c r="J289" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.2648829366804848E-2</v>
       </c>
       <c r="K289" s="5">
         <v>0.1021527904144343</v>
@@ -15153,7 +15219,7 @@
         <v>306784</v>
       </c>
       <c r="G290" s="3">
-        <v>0</v>
+        <v>196784</v>
       </c>
       <c r="H290" s="3">
         <v>15231</v>
@@ -15163,7 +15229,7 @@
       </c>
       <c r="J290" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.7399585332140822E-2</v>
       </c>
       <c r="K290" s="5">
         <v>8.4798594256149246E-2</v>
@@ -15198,7 +15264,7 @@
         <v>333480</v>
       </c>
       <c r="G291" s="3">
-        <v>0</v>
+        <v>204647</v>
       </c>
       <c r="H291" s="3">
         <v>15604</v>
@@ -15208,7 +15274,7 @@
       </c>
       <c r="J291" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.6248369142963249E-2</v>
       </c>
       <c r="K291" s="5">
         <v>7.9045410833963631E-2</v>
@@ -15243,7 +15309,7 @@
         <v>369374</v>
       </c>
       <c r="G292" s="3">
-        <v>0</v>
+        <v>211687</v>
       </c>
       <c r="H292" s="3">
         <v>16615</v>
@@ -15253,7 +15319,7 @@
       </c>
       <c r="J292" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.8488523149744666E-2</v>
       </c>
       <c r="K292" s="5">
         <v>8.8957966580963554E-2</v>
@@ -15288,7 +15354,7 @@
         <v>351732</v>
       </c>
       <c r="G293" s="3">
-        <v>0</v>
+        <v>180051</v>
       </c>
       <c r="H293" s="3">
         <v>14554</v>
@@ -15298,7 +15364,7 @@
       </c>
       <c r="J293" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.0832652970547231E-2</v>
       </c>
       <c r="K293" s="5">
         <v>9.6404481117215043E-2</v>
@@ -15333,7 +15399,7 @@
         <v>343158</v>
       </c>
       <c r="G294" s="3">
-        <v>0</v>
+        <v>201428</v>
       </c>
       <c r="H294" s="3">
         <v>16157</v>
@@ -15343,7 +15409,7 @@
       </c>
       <c r="J294" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.0212284290168204E-2</v>
       </c>
       <c r="K294" s="5">
         <v>0.1001464290404739</v>
@@ -15378,7 +15444,7 @@
         <v>348031</v>
       </c>
       <c r="G295" s="3">
-        <v>0</v>
+        <v>212633</v>
       </c>
       <c r="H295" s="3">
         <v>16556</v>
@@ -15388,7 +15454,7 @@
       </c>
       <c r="J295" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.7861855873735494E-2</v>
       </c>
       <c r="K295" s="5">
         <v>8.770398246851592E-2</v>
@@ -15423,7 +15489,7 @@
         <v>369720</v>
       </c>
       <c r="G296" s="3">
-        <v>0</v>
+        <v>232055</v>
       </c>
       <c r="H296" s="3">
         <v>16177</v>
@@ -15433,7 +15499,7 @@
       </c>
       <c r="J296" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.9711921742690308E-2</v>
       </c>
       <c r="K296" s="5">
         <v>9.019689105031467E-2</v>
@@ -15468,7 +15534,7 @@
         <v>427193</v>
       </c>
       <c r="G297" s="3">
-        <v>0</v>
+        <v>301517</v>
       </c>
       <c r="H297" s="3">
         <v>18077</v>
@@ -15478,7 +15544,7 @@
       </c>
       <c r="J297" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5.9953501792602074E-2</v>
       </c>
       <c r="K297" s="5">
         <v>8.1392533713773196E-2</v>
@@ -15513,7 +15579,7 @@
         <v>413406</v>
       </c>
       <c r="G298" s="3">
-        <v>0</v>
+        <v>224869</v>
       </c>
       <c r="H298" s="3">
         <v>17692</v>
@@ -15523,7 +15589,7 @@
       </c>
       <c r="J298" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.8676918561473574E-2</v>
       </c>
       <c r="K298" s="5">
         <v>0.1078043845406482</v>
@@ -15558,7 +15624,7 @@
         <v>364133</v>
       </c>
       <c r="G299" s="3">
-        <v>0</v>
+        <v>241041</v>
       </c>
       <c r="H299" s="3">
         <v>18804</v>
@@ -15568,7 +15634,7 @@
       </c>
       <c r="J299" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.8011624578391225E-2</v>
       </c>
       <c r="K299" s="5">
         <v>8.0001703222949333E-2</v>
@@ -15603,7 +15669,7 @@
         <v>487336</v>
       </c>
       <c r="G300" s="3">
-        <v>0</v>
+        <v>211972</v>
       </c>
       <c r="H300" s="3">
         <v>17089</v>
@@ -15613,7 +15679,7 @@
       </c>
       <c r="J300" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.061913837676675E-2</v>
       </c>
       <c r="K300" s="5">
         <v>9.4367924599765299E-2</v>
@@ -15648,7 +15714,7 @@
         <v>507357</v>
       </c>
       <c r="G301" s="3">
-        <v>0</v>
+        <v>231499</v>
       </c>
       <c r="H301" s="3">
         <v>18009</v>
@@ -15658,7 +15724,7 @@
       </c>
       <c r="J301" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.7792992626318044E-2</v>
       </c>
       <c r="K301" s="5">
         <v>7.7432601841640192E-2</v>
@@ -15693,7 +15759,7 @@
         <v>537943</v>
       </c>
       <c r="G302" s="3">
-        <v>0</v>
+        <v>257918</v>
       </c>
       <c r="H302" s="3">
         <v>20686</v>
@@ -15703,7 +15769,7 @@
       </c>
       <c r="J302" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.0203785699330801E-2</v>
       </c>
       <c r="K302" s="5">
         <v>0.1019281009667094</v>
@@ -15738,7 +15804,7 @@
         <v>523982</v>
       </c>
       <c r="G303" s="3">
-        <v>0</v>
+        <v>313000</v>
       </c>
       <c r="H303" s="3">
         <v>18422</v>
@@ -15748,7 +15814,7 @@
       </c>
       <c r="J303" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5.8856230031948883E-2</v>
       </c>
       <c r="K303" s="5">
         <v>8.0573845175147929E-2</v>
@@ -15783,7 +15849,7 @@
         <v>500811</v>
       </c>
       <c r="G304" s="3">
-        <v>0</v>
+        <v>316004</v>
       </c>
       <c r="H304" s="3">
         <v>20594</v>
@@ -15793,7 +15859,7 @@
       </c>
       <c r="J304" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6.5170061138466601E-2</v>
       </c>
       <c r="K304" s="5">
         <v>8.6848007458260171E-2</v>
@@ -15828,7 +15894,7 @@
         <v>557037</v>
       </c>
       <c r="G305" s="3">
-        <v>0</v>
+        <v>275270</v>
       </c>
       <c r="H305" s="3">
         <v>21029</v>
@@ -15838,7 +15904,7 @@
       </c>
       <c r="J305" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.6394085806662543E-2</v>
       </c>
       <c r="K305" s="5">
         <v>9.7709787781642674E-2</v>
@@ -15873,7 +15939,7 @@
         <v>585887</v>
       </c>
       <c r="G306" s="3">
-        <v>0</v>
+        <v>272309</v>
       </c>
       <c r="H306" s="3">
         <v>21588</v>
@@ -15883,7 +15949,7 @@
       </c>
       <c r="J306" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.9277585390126651E-2</v>
       </c>
       <c r="K306" s="5">
         <v>8.5518887246061798E-2</v>
@@ -15918,7 +15984,7 @@
         <v>595217</v>
       </c>
       <c r="G307" s="3">
-        <v>0</v>
+        <v>233636</v>
       </c>
       <c r="H307" s="3">
         <v>19155</v>
@@ -15928,7 +15994,7 @@
       </c>
       <c r="J307" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8.1986508928418564E-2</v>
       </c>
       <c r="K307" s="5">
         <v>8.3683885321049298E-2</v>
@@ -15963,7 +16029,7 @@
         <v>422810</v>
       </c>
       <c r="G308" s="3">
-        <v>0</v>
+        <v>239326</v>
       </c>
       <c r="H308" s="3">
         <v>18472</v>
@@ -15973,7 +16039,7 @@
       </c>
       <c r="J308" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.7183423447515109E-2</v>
       </c>
       <c r="K308" s="5">
         <v>8.3080406632258297E-2</v>
@@ -16008,7 +16074,7 @@
         <v>383390</v>
       </c>
       <c r="G309" s="3">
-        <v>0</v>
+        <v>228475</v>
       </c>
       <c r="H309" s="3">
         <v>17787</v>
@@ -16018,7 +16084,7 @@
       </c>
       <c r="J309" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.7850968377284169E-2</v>
       </c>
       <c r="K309" s="5">
         <v>7.9953711744235448E-2</v>
@@ -16602,7 +16668,7 @@
         <v>1100</v>
       </c>
       <c r="J322" s="5">
-        <f t="shared" ref="J322:J388" si="5">IFERROR(H322/G322,0)</f>
+        <f t="shared" ref="J322:J385" si="5">IFERROR(H322/G322,0)</f>
         <v>5.9799653005755113E-2</v>
       </c>
       <c r="K322" s="5">
@@ -18420,10 +18486,10 @@
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C363" s="3">
         <v>204</v>
@@ -18432,10 +18498,10 @@
         <v>266277</v>
       </c>
       <c r="E363" s="3">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F363" s="4">
-        <v>265633</v>
+        <v>266277</v>
       </c>
       <c r="G363" s="3">
         <v>111673</v>
@@ -18457,7 +18523,7 @@
         <v>0.42377511642964338</v>
       </c>
       <c r="M363" s="5">
-        <v>0.99180327868852458</v>
+        <v>1</v>
       </c>
       <c r="N363" s="3">
         <v>264</v>
@@ -18465,16 +18531,16 @@
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C364" s="3">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D364" s="4">
-        <v>272706</v>
+        <v>271605</v>
       </c>
       <c r="E364" s="3">
         <v>207</v>
@@ -18499,10 +18565,10 @@
         <v>0.10014269601360599</v>
       </c>
       <c r="L364" s="5">
-        <v>0.38001627870574289</v>
+        <v>0.37937770910165602</v>
       </c>
       <c r="M364" s="5">
-        <v>0.99669421487603316</v>
+        <v>0.99818181818181817</v>
       </c>
       <c r="N364" s="3">
         <v>322</v>
@@ -18510,10 +18576,10 @@
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C365" s="3">
         <v>165</v>
@@ -18522,10 +18588,10 @@
         <v>206380</v>
       </c>
       <c r="E365" s="3">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F365" s="4">
-        <v>203520</v>
+        <v>206380</v>
       </c>
       <c r="G365" s="3">
         <v>134115</v>
@@ -18547,7 +18613,7 @@
         <v>0.36895984794677872</v>
       </c>
       <c r="M365" s="5">
-        <v>0.99038461538461531</v>
+        <v>1</v>
       </c>
       <c r="N365" s="3">
         <v>381</v>
@@ -18555,10 +18621,10 @@
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C366" s="3">
         <v>179</v>
@@ -18600,10 +18666,10 @@
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C367" s="3">
         <v>219</v>
@@ -18645,16 +18711,16 @@
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C368" s="3">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D368" s="4">
-        <v>216537</v>
+        <v>214997</v>
       </c>
       <c r="E368" s="3">
         <v>173</v>
@@ -18679,10 +18745,10 @@
         <v>9.9058175737397461E-2</v>
       </c>
       <c r="L368" s="5">
-        <v>0.38989886892122327</v>
+        <v>0.37235500927210041</v>
       </c>
       <c r="M368" s="5">
-        <v>0.99152542372881358</v>
+        <v>1</v>
       </c>
       <c r="N368" s="3">
         <v>321</v>
@@ -18690,16 +18756,16 @@
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C369" s="3">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D369" s="4">
-        <v>235817</v>
+        <v>233977</v>
       </c>
       <c r="E369" s="3">
         <v>178</v>
@@ -18724,10 +18790,10 @@
         <v>9.3710131918303408E-2</v>
       </c>
       <c r="L369" s="5">
-        <v>0.41042302912746748</v>
+        <v>0.40966973345891772</v>
       </c>
       <c r="M369" s="5">
-        <v>0.98602150537634403</v>
+        <v>0.99193548387096764</v>
       </c>
       <c r="N369" s="3">
         <v>308</v>
@@ -18735,10 +18801,10 @@
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C370" s="3">
         <v>167</v>
@@ -18747,10 +18813,10 @@
         <v>213404</v>
       </c>
       <c r="E370" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F370" s="4">
-        <v>209414</v>
+        <v>213404</v>
       </c>
       <c r="G370" s="3">
         <v>150030</v>
@@ -18772,7 +18838,7 @@
         <v>0.39923434346529169</v>
       </c>
       <c r="M370" s="5">
-        <v>0.99315476190476193</v>
+        <v>1</v>
       </c>
       <c r="N370" s="3">
         <v>291</v>
@@ -18783,19 +18849,19 @@
         <v>533</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C371" s="3">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D371" s="4">
-        <v>251826</v>
+        <v>248936</v>
       </c>
       <c r="E371" s="3">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F371" s="4">
-        <v>245483</v>
+        <v>248936</v>
       </c>
       <c r="G371" s="3">
         <v>151890</v>
@@ -18814,10 +18880,10 @@
         <v>9.1767601293784459E-2</v>
       </c>
       <c r="L371" s="5">
-        <v>0.39336130266386649</v>
+        <v>0.39232203929374321</v>
       </c>
       <c r="M371" s="5">
-        <v>0.98270227631282381</v>
+        <v>1</v>
       </c>
       <c r="N371" s="3">
         <v>293</v>
@@ -18825,22 +18891,22 @@
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C372" s="3">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D372" s="4">
-        <v>276160</v>
+        <v>273260</v>
       </c>
       <c r="E372" s="3">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F372" s="4">
-        <v>271720</v>
+        <v>273260</v>
       </c>
       <c r="G372" s="3">
         <v>198840</v>
@@ -18859,10 +18925,10 @@
         <v>8.9512548342816453E-2</v>
       </c>
       <c r="L372" s="5">
-        <v>0.36714532687488882</v>
+        <v>0.36398743213804657</v>
       </c>
       <c r="M372" s="5">
-        <v>0.98518233179250136</v>
+        <v>1</v>
       </c>
       <c r="N372" s="3">
         <v>328</v>
@@ -18870,22 +18936,22 @@
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C373" s="3">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D373" s="4">
-        <v>233475</v>
+        <v>232525</v>
       </c>
       <c r="E373" s="3">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F373" s="4">
-        <v>228850</v>
+        <v>231175</v>
       </c>
       <c r="G373" s="3">
         <v>130475</v>
@@ -18904,10 +18970,10 @@
         <v>9.5580119392953133E-2</v>
       </c>
       <c r="L373" s="5">
-        <v>0.40744469429008662</v>
+        <v>0.40644469429008673</v>
       </c>
       <c r="M373" s="5">
-        <v>0.98751515151515168</v>
+        <v>0.996</v>
       </c>
       <c r="N373" s="3">
         <v>278</v>
@@ -18915,22 +18981,22 @@
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C374" s="3">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D374" s="4">
-        <v>223360</v>
+        <v>215974</v>
       </c>
       <c r="E374" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F374" s="4">
-        <v>209470</v>
+        <v>214390</v>
       </c>
       <c r="G374" s="3">
         <v>126100</v>
@@ -18949,10 +19015,10 @@
         <v>8.7738638395192747E-2</v>
       </c>
       <c r="L374" s="5">
-        <v>0.36943678969148541</v>
+        <v>0.36630283692338622</v>
       </c>
       <c r="M374" s="5">
-        <v>0.96913116123642429</v>
+        <v>0.99753694581280794</v>
       </c>
       <c r="N374" s="3">
         <v>302</v>
@@ -18960,22 +19026,22 @@
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C375" s="3">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D375" s="4">
-        <v>268226</v>
+        <v>260851</v>
       </c>
       <c r="E375" s="3">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F375" s="4">
-        <v>246051</v>
+        <v>254839</v>
       </c>
       <c r="G375" s="3">
         <v>122267</v>
@@ -18994,10 +19060,10 @@
         <v>9.5888389992608916E-2</v>
       </c>
       <c r="L375" s="5">
-        <v>0.3712795027568816</v>
+        <v>0.36300856877942589</v>
       </c>
       <c r="M375" s="5">
-        <v>0.93567776572994787</v>
+        <v>0.98231566820276495</v>
       </c>
       <c r="N375" s="3">
         <v>270</v>
@@ -19005,22 +19071,22 @@
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C376" s="3">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D376" s="4">
-        <v>251553</v>
+        <v>247123</v>
       </c>
       <c r="E376" s="3">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F376" s="4">
-        <v>238291</v>
+        <v>247123</v>
       </c>
       <c r="G376" s="3">
         <v>121131</v>
@@ -19039,10 +19105,10 @@
         <v>8.9883875894926663E-2</v>
       </c>
       <c r="L376" s="5">
-        <v>0.39392038471331092</v>
+        <v>0.39124639203931821</v>
       </c>
       <c r="M376" s="5">
-        <v>0.97570919276801649</v>
+        <v>1</v>
       </c>
       <c r="N376" s="3">
         <v>253</v>
@@ -19050,22 +19116,22 @@
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C377" s="3">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D377" s="4">
-        <v>239582</v>
+        <v>238662</v>
       </c>
       <c r="E377" s="3">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F377" s="4">
-        <v>231237</v>
+        <v>237122</v>
       </c>
       <c r="G377" s="3">
         <v>116461</v>
@@ -19084,10 +19150,10 @@
         <v>8.2929552174884E-2</v>
       </c>
       <c r="L377" s="5">
-        <v>0.3966982218820676</v>
+        <v>0.39619696874923549</v>
       </c>
       <c r="M377" s="5">
-        <v>0.96631089217296118</v>
+        <v>0.99753694581280794</v>
       </c>
       <c r="N377" s="3">
         <v>299</v>
@@ -19095,22 +19161,22 @@
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C378" s="3">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D378" s="4">
-        <v>276906</v>
+        <v>261466</v>
       </c>
       <c r="E378" s="3">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="F378" s="4">
-        <v>244336</v>
+        <v>260116</v>
       </c>
       <c r="G378" s="3">
         <v>124083</v>
@@ -19129,10 +19195,10 @@
         <v>0.1201572105570811</v>
       </c>
       <c r="L378" s="5">
-        <v>0.38049695819126289</v>
+        <v>0.35225593937907862</v>
       </c>
       <c r="M378" s="5">
-        <v>0.93108064774731447</v>
+        <v>0.99393939393939401</v>
       </c>
       <c r="N378" s="3">
         <v>279</v>
@@ -19140,22 +19206,22 @@
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C379" s="3">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D379" s="4">
-        <v>229847</v>
+        <v>220098</v>
       </c>
       <c r="E379" s="3">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="F379" s="4">
-        <v>194914</v>
+        <v>215992</v>
       </c>
       <c r="G379" s="3">
         <v>138541</v>
@@ -19174,10 +19240,10 @@
         <v>0.1018356749303705</v>
       </c>
       <c r="L379" s="5">
-        <v>0.31437734327041328</v>
+        <v>0.30498681853752763</v>
       </c>
       <c r="M379" s="5">
-        <v>0.90584816418149761</v>
+        <v>0.9896421845574388</v>
       </c>
       <c r="N379" s="3">
         <v>418</v>
@@ -19185,22 +19251,22 @@
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C380" s="3">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="D380" s="4">
-        <v>260490</v>
+        <v>236903</v>
       </c>
       <c r="E380" s="3">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="F380" s="4">
-        <v>200332</v>
+        <v>229802</v>
       </c>
       <c r="G380" s="3">
         <v>123681</v>
@@ -19219,10 +19285,10 @@
         <v>0.109912770760024</v>
       </c>
       <c r="L380" s="5">
-        <v>0.40066648792255449</v>
+        <v>0.38331412615111959</v>
       </c>
       <c r="M380" s="5">
-        <v>0.87225161669606122</v>
+        <v>0.98505747126436782</v>
       </c>
       <c r="N380" s="3">
         <v>309</v>
@@ -19230,22 +19296,22 @@
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C381" s="3">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D381" s="4">
-        <v>283086</v>
+        <v>273151</v>
       </c>
       <c r="E381" s="3">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="F381" s="4">
-        <v>231658</v>
+        <v>266706</v>
       </c>
       <c r="G381" s="3">
         <v>119369</v>
@@ -19264,10 +19330,10 @@
         <v>8.9433709004823905E-2</v>
       </c>
       <c r="L381" s="5">
-        <v>0.38137140647899709</v>
+        <v>0.37369008235392781</v>
       </c>
       <c r="M381" s="5">
-        <v>0.87928395401876602</v>
+        <v>0.99714781746031744</v>
       </c>
       <c r="N381" s="3">
         <v>291</v>
@@ -19275,22 +19341,22 @@
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C382" s="3">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D382" s="4">
-        <v>281489</v>
+        <v>273756</v>
       </c>
       <c r="E382" s="3">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="F382" s="4">
-        <v>206878</v>
+        <v>268162</v>
       </c>
       <c r="G382" s="3">
         <v>138831</v>
@@ -19309,10 +19375,10 @@
         <v>0.12646542665617719</v>
       </c>
       <c r="L382" s="5">
-        <v>0.39732867395923399</v>
+        <v>0.39161693492134558</v>
       </c>
       <c r="M382" s="5">
-        <v>0.87321099602011965</v>
+        <v>0.99244663382594411</v>
       </c>
       <c r="N382" s="3">
         <v>302</v>
@@ -19320,22 +19386,22 @@
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="C383" s="3">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D383" s="4">
-        <v>281400</v>
+        <v>271486</v>
       </c>
       <c r="E383" s="3">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="F383" s="4">
-        <v>203302</v>
+        <v>271486</v>
       </c>
       <c r="G383" s="3">
         <v>175633</v>
@@ -19354,10 +19420,10 @@
         <v>0.1105625473667334</v>
       </c>
       <c r="L383" s="5">
-        <v>0.43624051515164092</v>
+        <v>0.42255551812839609</v>
       </c>
       <c r="M383" s="5">
-        <v>0.84545528167977135</v>
+        <v>1</v>
       </c>
       <c r="N383" s="3">
         <v>292</v>
@@ -19365,22 +19431,22 @@
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C384" s="3">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D384" s="4">
-        <v>261005</v>
+        <v>251317</v>
       </c>
       <c r="E384" s="3">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="F384" s="4">
-        <v>175954</v>
+        <v>243482</v>
       </c>
       <c r="G384" s="3">
         <v>148592</v>
@@ -19399,10 +19465,10 @@
         <v>0.1101037090177618</v>
       </c>
       <c r="L384" s="5">
-        <v>0.37625763470917167</v>
+        <v>0.37488170871297299</v>
       </c>
       <c r="M384" s="5">
-        <v>0.85708845458532568</v>
+        <v>0.98988095238095231</v>
       </c>
       <c r="N384" s="3">
         <v>280</v>
@@ -19410,44 +19476,44 @@
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C385" s="3">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="D385" s="4">
-        <v>231809</v>
+        <v>215572</v>
       </c>
       <c r="E385" s="3">
-        <v>104</v>
+        <v>159</v>
       </c>
       <c r="F385" s="4">
-        <v>139620</v>
+        <v>210749</v>
       </c>
       <c r="G385" s="3">
         <v>157368</v>
       </c>
       <c r="H385" s="3">
-        <v>10519</v>
+        <v>10523</v>
       </c>
       <c r="I385" s="3">
         <v>748</v>
       </c>
       <c r="J385" s="5">
         <f t="shared" si="5"/>
-        <v>6.6843322657719487E-2</v>
+        <v>6.6868740785928527E-2</v>
       </c>
       <c r="K385" s="5">
-        <v>8.7245635411950767E-2</v>
+        <v>8.7236770794156232E-2</v>
       </c>
       <c r="L385" s="5">
-        <v>0.42836381704104781</v>
+        <v>0.40959844848759153</v>
       </c>
       <c r="M385" s="5">
-        <v>0.7691382030667745</v>
+        <v>1</v>
       </c>
       <c r="N385" s="3">
         <v>320</v>
@@ -19455,22 +19521,22 @@
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C386" s="3">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D386" s="4">
-        <v>289332</v>
+        <v>281606</v>
       </c>
       <c r="E386" s="3">
-        <v>98</v>
+        <v>194</v>
       </c>
       <c r="F386" s="4">
-        <v>127854</v>
+        <v>266163</v>
       </c>
       <c r="G386" s="3">
         <v>164299</v>
@@ -19482,17 +19548,17 @@
         <v>900</v>
       </c>
       <c r="J386" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J386:J401" si="6">IFERROR(H386/G386,0)</f>
         <v>6.6488536144468313E-2</v>
       </c>
       <c r="K386" s="5">
         <v>9.7846990519253454E-2</v>
       </c>
       <c r="L386" s="5">
-        <v>0.47408505172930582</v>
+        <v>0.46004261630015159</v>
       </c>
       <c r="M386" s="5">
-        <v>0.68993180420727063</v>
+        <v>0.97030460858585854</v>
       </c>
       <c r="N386" s="3">
         <v>314</v>
@@ -19500,44 +19566,44 @@
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C387" s="3">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D387" s="4">
-        <v>269046</v>
+        <v>255970</v>
       </c>
       <c r="E387" s="3">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="F387" s="4">
-        <v>40837</v>
+        <v>247742</v>
       </c>
       <c r="G387" s="3">
         <v>183759</v>
       </c>
       <c r="H387" s="3">
-        <v>11885</v>
+        <v>11886</v>
       </c>
       <c r="I387" s="3">
         <v>1006</v>
       </c>
       <c r="J387" s="5">
-        <f t="shared" si="5"/>
-        <v>6.467710425067616E-2</v>
+        <f t="shared" si="6"/>
+        <v>6.4682546161004356E-2</v>
       </c>
       <c r="K387" s="5">
-        <v>0.11665644518756919</v>
+        <v>0.1166496758131528</v>
       </c>
       <c r="L387" s="5">
-        <v>0.35460677404251789</v>
+        <v>0.34884489980286798</v>
       </c>
       <c r="M387" s="5">
-        <v>0.48716356107660452</v>
+        <v>0.98046387154326498</v>
       </c>
       <c r="N387" s="3">
         <v>369</v>
@@ -19545,51 +19611,636 @@
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C388" s="3">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="D388" s="4">
-        <v>313926</v>
+        <v>297715</v>
       </c>
       <c r="E388" s="3">
-        <v>2</v>
+        <v>217</v>
       </c>
       <c r="F388" s="4">
-        <v>2573</v>
+        <v>290744</v>
       </c>
       <c r="G388" s="3">
-        <v>163273</v>
+        <v>163845</v>
       </c>
       <c r="H388" s="3">
-        <v>10920</v>
+        <v>10921</v>
       </c>
       <c r="I388" s="3">
         <v>925</v>
       </c>
       <c r="J388" s="5">
-        <f t="shared" si="5"/>
-        <v>6.6881848192903909E-2</v>
+        <f t="shared" si="6"/>
+        <v>6.6654460007934332E-2</v>
       </c>
       <c r="K388" s="5">
-        <v>0.10346821238271341</v>
+        <v>0.1034652590066764</v>
       </c>
       <c r="L388" s="5">
-        <v>0.38318192947844132</v>
+        <v>0.37321423047198671</v>
       </c>
       <c r="M388" s="5">
-        <v>0.3125</v>
+        <v>0.97862112586970273</v>
       </c>
       <c r="N388" s="3">
         <v>307</v>
       </c>
     </row>
+    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A389" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C389" s="3">
+        <v>205</v>
+      </c>
+      <c r="D389" s="4">
+        <v>277557</v>
+      </c>
+      <c r="E389" s="3">
+        <v>197</v>
+      </c>
+      <c r="F389" s="4">
+        <v>263540</v>
+      </c>
+      <c r="G389" s="3">
+        <v>154418</v>
+      </c>
+      <c r="H389" s="3">
+        <v>10766</v>
+      </c>
+      <c r="I389" s="3">
+        <v>885</v>
+      </c>
+      <c r="J389" s="5">
+        <f t="shared" si="6"/>
+        <v>6.9719851312670805E-2</v>
+      </c>
+      <c r="K389" s="5">
+        <v>0.12433589661866171</v>
+      </c>
+      <c r="L389" s="5">
+        <v>0.35548153098175828</v>
+      </c>
+      <c r="M389" s="5">
+        <v>0.96845878136200714</v>
+      </c>
+      <c r="N389" s="3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A390" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="C390" s="3">
+        <v>260</v>
+      </c>
+      <c r="D390" s="4">
+        <v>357636</v>
+      </c>
+      <c r="E390" s="3">
+        <v>237</v>
+      </c>
+      <c r="F390" s="4">
+        <v>323338</v>
+      </c>
+      <c r="G390" s="3">
+        <v>285087</v>
+      </c>
+      <c r="H390" s="3">
+        <v>14062</v>
+      </c>
+      <c r="I390" s="3">
+        <v>1108</v>
+      </c>
+      <c r="J390" s="5">
+        <f t="shared" si="6"/>
+        <v>4.9325293682279447E-2</v>
+      </c>
+      <c r="K390" s="5">
+        <v>0.1004586291550723</v>
+      </c>
+      <c r="L390" s="5">
+        <v>0.39029455002853403</v>
+      </c>
+      <c r="M390" s="5">
+        <v>0.96361441798941794</v>
+      </c>
+      <c r="N390" s="3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="391" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A391" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C391" s="3">
+        <v>257</v>
+      </c>
+      <c r="D391" s="4">
+        <v>359749</v>
+      </c>
+      <c r="E391" s="3">
+        <v>235</v>
+      </c>
+      <c r="F391" s="4">
+        <v>328435</v>
+      </c>
+      <c r="G391" s="3">
+        <v>161464</v>
+      </c>
+      <c r="H391" s="3">
+        <v>11108</v>
+      </c>
+      <c r="I391" s="3">
+        <v>923</v>
+      </c>
+      <c r="J391" s="5">
+        <f t="shared" si="6"/>
+        <v>6.8795520983005495E-2</v>
+      </c>
+      <c r="K391" s="5">
+        <v>9.9668969736187996E-2</v>
+      </c>
+      <c r="L391" s="5">
+        <v>0.51578898147428442</v>
+      </c>
+      <c r="M391" s="5">
+        <v>0.94311669750914406</v>
+      </c>
+      <c r="N391" s="3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A392" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C392" s="3">
+        <v>225</v>
+      </c>
+      <c r="D392" s="4">
+        <v>315735</v>
+      </c>
+      <c r="E392" s="3">
+        <v>201</v>
+      </c>
+      <c r="F392" s="4">
+        <v>275133</v>
+      </c>
+      <c r="G392" s="3">
+        <v>164423</v>
+      </c>
+      <c r="H392" s="3">
+        <v>11936</v>
+      </c>
+      <c r="I392" s="3">
+        <v>1023</v>
+      </c>
+      <c r="J392" s="5">
+        <f t="shared" si="6"/>
+        <v>7.2593250336023554E-2</v>
+      </c>
+      <c r="K392" s="5">
+        <v>0.1140514288467032</v>
+      </c>
+      <c r="L392" s="5">
+        <v>0.36634707194642968</v>
+      </c>
+      <c r="M392" s="5">
+        <v>0.93475789142785193</v>
+      </c>
+      <c r="N392" s="3">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A393" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C393" s="3">
+        <v>281</v>
+      </c>
+      <c r="D393" s="4">
+        <v>383506</v>
+      </c>
+      <c r="E393" s="3">
+        <v>236</v>
+      </c>
+      <c r="F393" s="4">
+        <v>326044</v>
+      </c>
+      <c r="G393" s="3">
+        <v>156070</v>
+      </c>
+      <c r="H393" s="3">
+        <v>12110</v>
+      </c>
+      <c r="I393" s="3">
+        <v>1125</v>
+      </c>
+      <c r="J393" s="5">
+        <f t="shared" si="6"/>
+        <v>7.7593387582495038E-2</v>
+      </c>
+      <c r="K393" s="5">
+        <v>0.1095664702829709</v>
+      </c>
+      <c r="L393" s="5">
+        <v>0.38268805813724022</v>
+      </c>
+      <c r="M393" s="5">
+        <v>0.90179686827284089</v>
+      </c>
+      <c r="N393" s="3">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A394" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C394" s="3">
+        <v>310</v>
+      </c>
+      <c r="D394" s="4">
+        <v>427393</v>
+      </c>
+      <c r="E394" s="3">
+        <v>259</v>
+      </c>
+      <c r="F394" s="4">
+        <v>351997</v>
+      </c>
+      <c r="G394" s="3">
+        <v>261558</v>
+      </c>
+      <c r="H394" s="3">
+        <v>15641</v>
+      </c>
+      <c r="I394" s="3">
+        <v>1455</v>
+      </c>
+      <c r="J394" s="5">
+        <f t="shared" si="6"/>
+        <v>5.9799356165745263E-2</v>
+      </c>
+      <c r="K394" s="5">
+        <v>0.1013038725442638</v>
+      </c>
+      <c r="L394" s="5">
+        <v>0.33148186854976219</v>
+      </c>
+      <c r="M394" s="5">
+        <v>0.90751176927647526</v>
+      </c>
+      <c r="N394" s="3">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A395" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C395" s="3">
+        <v>281</v>
+      </c>
+      <c r="D395" s="4">
+        <v>368683</v>
+      </c>
+      <c r="E395" s="3">
+        <v>222</v>
+      </c>
+      <c r="F395" s="4">
+        <v>291906</v>
+      </c>
+      <c r="G395" s="3">
+        <v>280981</v>
+      </c>
+      <c r="H395" s="3">
+        <v>15970</v>
+      </c>
+      <c r="I395" s="3">
+        <v>1457</v>
+      </c>
+      <c r="J395" s="5">
+        <f t="shared" si="6"/>
+        <v>5.6836583256519121E-2</v>
+      </c>
+      <c r="K395" s="5">
+        <v>8.7240565442410614E-2</v>
+      </c>
+      <c r="L395" s="5">
+        <v>0.36845712071091302</v>
+      </c>
+      <c r="M395" s="5">
+        <v>0.84282101913680862</v>
+      </c>
+      <c r="N395" s="3">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A396" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C396" s="3">
+        <v>323</v>
+      </c>
+      <c r="D396" s="4">
+        <v>443629</v>
+      </c>
+      <c r="E396" s="3">
+        <v>227</v>
+      </c>
+      <c r="F396" s="4">
+        <v>312903</v>
+      </c>
+      <c r="G396" s="3">
+        <v>259729</v>
+      </c>
+      <c r="H396" s="3">
+        <v>15737</v>
+      </c>
+      <c r="I396" s="3">
+        <v>1408</v>
+      </c>
+      <c r="J396" s="5">
+        <f t="shared" si="6"/>
+        <v>6.0590076579819734E-2</v>
+      </c>
+      <c r="K396" s="5">
+        <v>9.4470065980079718E-2</v>
+      </c>
+      <c r="L396" s="5">
+        <v>0.36807394936899629</v>
+      </c>
+      <c r="M396" s="5">
+        <v>0.75931665965118222</v>
+      </c>
+      <c r="N396" s="3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="397" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A397" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C397" s="3">
+        <v>289</v>
+      </c>
+      <c r="D397" s="4">
+        <v>421288</v>
+      </c>
+      <c r="E397" s="3">
+        <v>182</v>
+      </c>
+      <c r="F397" s="4">
+        <v>254990</v>
+      </c>
+      <c r="G397" s="3">
+        <v>277299</v>
+      </c>
+      <c r="H397" s="3">
+        <v>17463</v>
+      </c>
+      <c r="I397" s="3">
+        <v>1581</v>
+      </c>
+      <c r="J397" s="5">
+        <f t="shared" si="6"/>
+        <v>6.2975344303441413E-2</v>
+      </c>
+      <c r="K397" s="5">
+        <v>9.3995212385867874E-2</v>
+      </c>
+      <c r="L397" s="5">
+        <v>0.30803238697466723</v>
+      </c>
+      <c r="M397" s="5">
+        <v>0.74244548554893386</v>
+      </c>
+      <c r="N397" s="3">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="398" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A398" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C398" s="3">
+        <v>320</v>
+      </c>
+      <c r="D398" s="4">
+        <v>448713</v>
+      </c>
+      <c r="E398" s="3">
+        <v>168</v>
+      </c>
+      <c r="F398" s="4">
+        <v>230290</v>
+      </c>
+      <c r="G398" s="3">
+        <v>273965</v>
+      </c>
+      <c r="H398" s="3">
+        <v>17040</v>
+      </c>
+      <c r="I398" s="3">
+        <v>1579</v>
+      </c>
+      <c r="J398" s="5">
+        <f t="shared" si="6"/>
+        <v>6.2197725986896137E-2</v>
+      </c>
+      <c r="K398" s="5">
+        <v>9.5454933090504207E-2</v>
+      </c>
+      <c r="L398" s="5">
+        <v>0.31083388972035447</v>
+      </c>
+      <c r="M398" s="5">
+        <v>0.6614412777718286</v>
+      </c>
+      <c r="N398" s="3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="399" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A399" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="C399" s="3">
+        <v>294</v>
+      </c>
+      <c r="D399" s="4">
+        <v>428104</v>
+      </c>
+      <c r="E399" s="3">
+        <v>116</v>
+      </c>
+      <c r="F399" s="4">
+        <v>175645</v>
+      </c>
+      <c r="G399" s="3">
+        <v>321073</v>
+      </c>
+      <c r="H399" s="3">
+        <v>18947</v>
+      </c>
+      <c r="I399" s="3">
+        <v>1572</v>
+      </c>
+      <c r="J399" s="5">
+        <f t="shared" si="6"/>
+        <v>5.9011502057164572E-2</v>
+      </c>
+      <c r="K399" s="5">
+        <v>7.9207847993796321E-2</v>
+      </c>
+      <c r="L399" s="5">
+        <v>0.26400954768882312</v>
+      </c>
+      <c r="M399" s="5">
+        <v>0.58927783778917997</v>
+      </c>
+      <c r="N399" s="3">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="400" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A400" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="C400" s="3">
+        <v>282</v>
+      </c>
+      <c r="D400" s="4">
+        <v>409275</v>
+      </c>
+      <c r="E400" s="3">
+        <v>44</v>
+      </c>
+      <c r="F400" s="4">
+        <v>61706</v>
+      </c>
+      <c r="G400" s="3">
+        <v>401735</v>
+      </c>
+      <c r="H400" s="3">
+        <v>19372</v>
+      </c>
+      <c r="I400" s="3">
+        <v>1519</v>
+      </c>
+      <c r="J400" s="5">
+        <f t="shared" si="6"/>
+        <v>4.8220842097402516E-2</v>
+      </c>
+      <c r="K400" s="5">
+        <v>8.1860823022144522E-2</v>
+      </c>
+      <c r="L400" s="5">
+        <v>0.29426909350601732</v>
+      </c>
+      <c r="M400" s="5">
+        <v>0.39960593718586052</v>
+      </c>
+      <c r="N400" s="3">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="401" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A401" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C401" s="3">
+        <v>233</v>
+      </c>
+      <c r="D401" s="4">
+        <v>336429</v>
+      </c>
+      <c r="E401" s="3">
+        <v>1</v>
+      </c>
+      <c r="F401" s="4">
+        <v>1652</v>
+      </c>
+      <c r="G401" s="3">
+        <v>198749</v>
+      </c>
+      <c r="H401" s="3">
+        <v>11572</v>
+      </c>
+      <c r="I401" s="3">
+        <v>1016</v>
+      </c>
+      <c r="J401" s="5">
+        <f t="shared" si="6"/>
+        <v>5.8224192322980241E-2</v>
+      </c>
+      <c r="K401" s="5">
+        <v>9.016908250725196E-2</v>
+      </c>
+      <c r="L401" s="5">
+        <v>0.35517403708995687</v>
+      </c>
+      <c r="M401" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="N401" s="3">
+        <v>255</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C3:D388">
+  <conditionalFormatting sqref="C3:D401">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>C3&gt;C2</formula>
     </cfRule>
@@ -19597,7 +20248,7 @@
       <formula>C3&lt;C2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G388">
+  <conditionalFormatting sqref="G3:G401">
     <cfRule type="expression" dxfId="3" priority="5">
       <formula>G3&gt;G2</formula>
     </cfRule>
@@ -19605,7 +20256,7 @@
       <formula>G3&lt;G2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:L388">
+  <conditionalFormatting sqref="I3:L401">
     <cfRule type="expression" dxfId="1" priority="7">
       <formula>I3&gt;I2</formula>
     </cfRule>
